--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/atakanemre/KMRProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atakan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D87CA4-D3AF-7546-8C5B-1DAB1E51F1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0325E5-E194-4062-8369-37CEDC3ECEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2720" windowWidth="30240" windowHeight="15340" xr2:uid="{7DFB6778-6F44-4552-81E5-A923E53590E6}"/>
+    <workbookView xWindow="4725" yWindow="1380" windowWidth="20475" windowHeight="18885" xr2:uid="{7DFB6778-6F44-4552-81E5-A923E53590E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
   <si>
     <t>BMI</t>
   </si>
@@ -331,6 +331,15 @@
   <si>
     <t>Month_1</t>
   </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
 </sst>
 </file>
 
@@ -388,7 +397,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -411,11 +420,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -449,6 +471,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -783,35 +814,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0EAAC3D-3553-4490-9689-67DC3C4D643F}">
-  <dimension ref="A1:AU995"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AW995"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" customWidth="1"/>
-    <col min="3" max="3" width="31.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1640625" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="28" max="28" width="16.1640625" customWidth="1"/>
-    <col min="29" max="29" width="15.83203125" customWidth="1"/>
-    <col min="30" max="30" width="15.6640625" customWidth="1"/>
-    <col min="31" max="33" width="14.6640625" customWidth="1"/>
-    <col min="34" max="34" width="15.1640625" customWidth="1"/>
-    <col min="35" max="36" width="14.5" customWidth="1"/>
-    <col min="37" max="37" width="13.6640625" customWidth="1"/>
-    <col min="38" max="38" width="15.33203125" customWidth="1"/>
-    <col min="39" max="39" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="1"/>
+    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="28" max="28" width="16.140625" customWidth="1"/>
+    <col min="29" max="29" width="15.85546875" customWidth="1"/>
+    <col min="30" max="30" width="15.7109375" customWidth="1"/>
+    <col min="31" max="33" width="14.7109375" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" customWidth="1"/>
+    <col min="37" max="37" width="13.7109375" customWidth="1"/>
+    <col min="38" max="38" width="15.28515625" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.6640625" customWidth="1"/>
-    <col min="42" max="42" width="19.33203125" customWidth="1"/>
-    <col min="43" max="43" width="15.5" customWidth="1"/>
-    <col min="44" max="44" width="17.1640625" customWidth="1"/>
+    <col min="41" max="41" width="13.7109375" customWidth="1"/>
+    <col min="42" max="42" width="19.28515625" customWidth="1"/>
+    <col min="43" max="43" width="15.42578125" customWidth="1"/>
+    <col min="44" max="44" width="17.140625" customWidth="1"/>
     <col min="45" max="45" width="14" customWidth="1"/>
-    <col min="46" max="46" width="17.5" customWidth="1"/>
-    <col min="47" max="47" width="15.83203125" customWidth="1"/>
+    <col min="46" max="46" width="17.42578125" customWidth="1"/>
+    <col min="47" max="47" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>69</v>
       </c>
@@ -954,7 +986,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>22</v>
       </c>
@@ -1087,7 +1119,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>31</v>
       </c>
@@ -1212,7 +1244,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>52</v>
       </c>
@@ -1331,7 +1363,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>16</v>
       </c>
@@ -1446,7 +1478,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>58</v>
       </c>
@@ -1565,7 +1597,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>31</v>
       </c>
@@ -1636,7 +1668,7 @@
       <c r="AT7" s="5"/>
       <c r="AU7" s="5"/>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>44</v>
       </c>
@@ -1684,7 +1716,9 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6">
+        <v>5.7090719499478624</v>
+      </c>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -1757,7 +1791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>52</v>
       </c>
@@ -1878,7 +1912,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>50</v>
       </c>
@@ -2009,7 +2043,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>41</v>
       </c>
@@ -2134,7 +2168,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>42</v>
       </c>
@@ -2235,7 +2269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -2328,7 +2362,7 @@
       </c>
       <c r="AU13" s="5"/>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>25</v>
       </c>
@@ -2386,7 +2420,9 @@
       <c r="Y14" s="6">
         <v>0</v>
       </c>
-      <c r="Z14" s="6"/>
+      <c r="Z14" s="6">
+        <v>9.9680305645176479E-2</v>
+      </c>
       <c r="AA14" s="6"/>
       <c r="AB14" s="5">
         <v>0.64</v>
@@ -2449,7 +2485,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>25</v>
       </c>
@@ -2503,10 +2539,16 @@
       </c>
       <c r="V15" s="6"/>
       <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
+      <c r="X15" s="6">
+        <v>7.0476467548706762E-2</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>6.2570470623921931E-2</v>
+      </c>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
+      <c r="AA15" s="6">
+        <v>0.51700143421363498</v>
+      </c>
       <c r="AB15" s="5">
         <v>1.18</v>
       </c>
@@ -2568,7 +2610,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>39</v>
       </c>
@@ -2683,7 +2725,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>28</v>
       </c>
@@ -2734,7 +2776,9 @@
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
+      <c r="AA17" s="6">
+        <v>5.8686611341330575E-2</v>
+      </c>
       <c r="AB17" s="5">
         <v>1.55</v>
       </c>
@@ -2796,7 +2840,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>43</v>
       </c>
@@ -2851,9 +2895,15 @@
       <c r="X18" s="6">
         <v>2.1720243266724587E-2</v>
       </c>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
+      <c r="Y18" s="6">
+        <v>3.336298932384342E-2</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>3.550616020759547E-2</v>
+      </c>
+      <c r="AA18" s="6">
+        <v>2.5293737953626685E-2</v>
+      </c>
       <c r="AB18" s="5">
         <v>1.18</v>
       </c>
@@ -2915,7 +2965,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>64</v>
       </c>
@@ -2966,9 +3016,13 @@
       </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
+      <c r="Y19" s="6">
+        <v>0.18308208112175875</v>
+      </c>
       <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
+      <c r="AA19" s="6">
+        <v>0.29744650277646167</v>
+      </c>
       <c r="AB19" s="5">
         <v>1.9</v>
       </c>
@@ -3030,7 +3084,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>41</v>
       </c>
@@ -3083,11 +3137,19 @@
         <v>0.24177864978265742</v>
       </c>
       <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
+      <c r="W20" s="6">
+        <v>7.3247172902135074E-2</v>
+      </c>
+      <c r="X20" s="6">
+        <v>0.20696706570687992</v>
+      </c>
       <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AA20" s="6"/>
+      <c r="Z20" s="6">
+        <v>7.3661160488188238E-3</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>0.20687590309198398</v>
+      </c>
       <c r="AB20" s="5">
         <v>1.97</v>
       </c>
@@ -3145,7 +3207,7 @@
       <c r="AT20" s="5"/>
       <c r="AU20" s="5"/>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>41</v>
       </c>
@@ -3254,7 +3316,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>32</v>
       </c>
@@ -3375,7 +3437,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>43</v>
       </c>
@@ -3494,7 +3556,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>6</v>
       </c>
@@ -3595,7 +3657,7 @@
       </c>
       <c r="AU24" s="5"/>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>51</v>
       </c>
@@ -3662,7 +3724,9 @@
       <c r="Z25" s="6">
         <v>0.25352874692611926</v>
       </c>
-      <c r="AA25" s="6"/>
+      <c r="AA25" s="6">
+        <v>0.12173454193645131</v>
+      </c>
       <c r="AB25" s="5">
         <v>1.1200000000000001</v>
       </c>
@@ -3720,7 +3784,7 @@
       <c r="AT25" s="5"/>
       <c r="AU25" s="5"/>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>50</v>
       </c>
@@ -3781,9 +3845,13 @@
         <v>7.399831956193112E-2</v>
       </c>
       <c r="X26" s="6"/>
-      <c r="Y26" s="6"/>
+      <c r="Y26" s="6">
+        <v>4.9582194749072057E-2</v>
+      </c>
       <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
+      <c r="AA26" s="6">
+        <v>0.23130292458138044</v>
+      </c>
       <c r="AB26" s="5">
         <v>0.85</v>
       </c>
@@ -3841,7 +3909,7 @@
       <c r="AT26" s="5"/>
       <c r="AU26" s="5"/>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>34</v>
       </c>
@@ -3898,7 +3966,9 @@
       <c r="Z27" s="6">
         <v>0.11011782437672391</v>
       </c>
-      <c r="AA27" s="6"/>
+      <c r="AA27" s="6">
+        <v>2.5265353216906317E-2</v>
+      </c>
       <c r="AB27" s="5">
         <v>1.32</v>
       </c>
@@ -3956,7 +4026,7 @@
       <c r="AT27" s="5"/>
       <c r="AU27" s="5"/>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>51</v>
       </c>
@@ -4015,9 +4085,13 @@
       <c r="X28" s="6">
         <v>2.4440457455834605E-2</v>
       </c>
-      <c r="Y28" s="6"/>
+      <c r="Y28" s="6">
+        <v>0.10420557084766417</v>
+      </c>
       <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
+      <c r="AA28" s="6">
+        <v>8.1914563583692826E-2</v>
+      </c>
       <c r="AB28" s="5">
         <v>2.5099999999999998</v>
       </c>
@@ -4075,7 +4149,7 @@
       <c r="AT28" s="5"/>
       <c r="AU28" s="5"/>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>12</v>
       </c>
@@ -4130,8 +4204,12 @@
       </c>
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
+      <c r="Y29" s="6">
+        <v>0.12520547370043228</v>
+      </c>
+      <c r="Z29" s="6">
+        <v>0.16023905085849069</v>
+      </c>
       <c r="AA29" s="6"/>
       <c r="AB29" s="5">
         <v>0.69</v>
@@ -4172,7 +4250,7 @@
       <c r="AT29" s="5"/>
       <c r="AU29" s="5"/>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>47</v>
       </c>
@@ -4228,10 +4306,18 @@
       <c r="W30" s="6">
         <v>0.35936677445307619</v>
       </c>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
+      <c r="X30" s="6">
+        <v>9.2008121725145081E-2</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>3.9346898855450202E-2</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>0.47460581085441328</v>
+      </c>
+      <c r="AA30" s="6">
+        <v>3.4344766671826926E-2</v>
+      </c>
       <c r="AB30" s="5">
         <v>1.84</v>
       </c>
@@ -4289,7 +4375,7 @@
       <c r="AT30" s="5"/>
       <c r="AU30" s="5"/>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>54</v>
       </c>
@@ -4343,9 +4429,15 @@
         <v>5.8638515442500892E-2</v>
       </c>
       <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
+      <c r="X31" s="6">
+        <v>7.4484240060200615E-2</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>0.15389914852346939</v>
+      </c>
+      <c r="Z31" s="6">
+        <v>7.2123839018427935E-2</v>
+      </c>
       <c r="AA31" s="6"/>
       <c r="AB31" s="5">
         <v>1.61</v>
@@ -4404,7 +4496,7 @@
       <c r="AT31" s="5"/>
       <c r="AU31" s="5"/>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>20</v>
       </c>
@@ -4463,9 +4555,15 @@
       <c r="V32" s="6">
         <v>0.1419748432891238</v>
       </c>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
+      <c r="W32" s="6">
+        <v>1.8050541516245487E-2</v>
+      </c>
+      <c r="X32" s="6">
+        <v>4.3634487501510305E-2</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>1.603866069100451E-2</v>
+      </c>
       <c r="Z32" s="6"/>
       <c r="AA32" s="6"/>
       <c r="AB32" s="5">
@@ -4525,7 +4623,7 @@
       <c r="AT32" s="5"/>
       <c r="AU32" s="5"/>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -4574,8 +4672,12 @@
       <c r="V33" s="6">
         <v>0.39144767735322844</v>
       </c>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
+      <c r="W33" s="6">
+        <v>3.1821797931583136E-2</v>
+      </c>
+      <c r="X33" s="6">
+        <v>0.13248383515831061</v>
+      </c>
       <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
@@ -4636,7 +4738,7 @@
       <c r="AT33" s="5"/>
       <c r="AU33" s="5"/>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>28</v>
       </c>
@@ -4689,8 +4791,12 @@
       <c r="T34" s="6">
         <v>0.23468952787962069</v>
       </c>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
+      <c r="U34" s="6">
+        <v>0.17573892805001276</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.11545175105368022</v>
+      </c>
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
       <c r="Y34" s="6"/>
@@ -4753,7 +4859,7 @@
       <c r="AT34" s="5"/>
       <c r="AU34" s="5"/>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>19</v>
       </c>
@@ -4801,11 +4907,17 @@
         <v>8.8933895901471868E-2</v>
       </c>
       <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
+      <c r="T35" s="6">
+        <v>0.12838391129769219</v>
+      </c>
+      <c r="U35" s="6">
+        <v>0.17281985683206191</v>
+      </c>
       <c r="V35" s="6"/>
       <c r="W35" s="6"/>
-      <c r="X35" s="6"/>
+      <c r="X35" s="6">
+        <v>0.14509920517529817</v>
+      </c>
       <c r="Y35" s="6"/>
       <c r="Z35" s="6"/>
       <c r="AA35" s="6"/>
@@ -4866,7 +4978,7 @@
       <c r="AT35" s="5"/>
       <c r="AU35" s="5"/>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>49</v>
       </c>
@@ -4916,7 +5028,9 @@
       <c r="U36" s="6"/>
       <c r="V36" s="6"/>
       <c r="W36" s="6"/>
-      <c r="X36" s="6"/>
+      <c r="X36" s="6">
+        <v>1.5174726732151715</v>
+      </c>
       <c r="Y36" s="6"/>
       <c r="Z36" s="6"/>
       <c r="AA36" s="6"/>
@@ -4977,7 +5091,7 @@
       <c r="AT36" s="5"/>
       <c r="AU36" s="5"/>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>16</v>
       </c>
@@ -5068,7 +5182,7 @@
       <c r="AT37" s="5"/>
       <c r="AU37" s="5"/>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>18</v>
       </c>
@@ -5117,10 +5231,18 @@
       <c r="T38" s="6">
         <v>0.39288663540073221</v>
       </c>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
-      <c r="X38" s="6"/>
+      <c r="U38" s="6">
+        <v>8.8869659825353678E-2</v>
+      </c>
+      <c r="V38" s="6">
+        <v>0.17110201281136173</v>
+      </c>
+      <c r="W38" s="6">
+        <v>0.87676644207110432</v>
+      </c>
+      <c r="X38" s="6">
+        <v>0.23309827298511329</v>
+      </c>
       <c r="Y38" s="6"/>
       <c r="Z38" s="6"/>
       <c r="AA38" s="6"/>
@@ -5181,7 +5303,7 @@
       <c r="AT38" s="5"/>
       <c r="AU38" s="5"/>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>71</v>
       </c>
@@ -5226,7 +5348,7 @@
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6">
-        <v>8.1230929116366701E-2</v>
+        <v>0.27674277400162661</v>
       </c>
       <c r="Q39" s="6">
         <v>0.12643633270284216</v>
@@ -5234,9 +5356,15 @@
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
+      <c r="U39" s="6">
+        <v>4.260135422382505E-2</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.15443372710861136</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.75886379700101647</v>
+      </c>
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
@@ -5298,7 +5426,7 @@
       <c r="AT39" s="5"/>
       <c r="AU39" s="5"/>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>52</v>
       </c>
@@ -5353,8 +5481,12 @@
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
       <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
+      <c r="U40" s="6">
+        <v>0.19494834901343047</v>
+      </c>
+      <c r="V40" s="6">
+        <v>0.15802698511697921</v>
+      </c>
       <c r="W40" s="6"/>
       <c r="X40" s="6"/>
       <c r="Y40" s="6"/>
@@ -5417,82 +5549,84 @@
       <c r="AT40" s="5"/>
       <c r="AU40" s="5"/>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
         <v>13</v>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="15">
         <v>20.5</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="16">
         <v>2.3244143517301996</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="16">
         <v>2.5464072957629216</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="16">
         <v>2.7081367183262275</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="16">
         <v>0.23647492316093396</v>
       </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6">
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16">
         <v>0.34962132542822633</v>
       </c>
-      <c r="N41" s="6">
+      <c r="N41" s="16">
         <v>0.33987233742142409</v>
       </c>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="6"/>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
-      <c r="AA41" s="6"/>
-      <c r="AB41" s="5">
+      <c r="O41" s="16"/>
+      <c r="P41" s="16"/>
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="17">
         <v>2.61</v>
       </c>
-      <c r="AC41" s="5"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="5"/>
-      <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
-      <c r="AH41" s="5"/>
-      <c r="AI41" s="5"/>
-      <c r="AJ41" s="5"/>
-      <c r="AK41" s="5"/>
-      <c r="AL41" s="5"/>
-      <c r="AM41" s="5"/>
-      <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
-      <c r="AP41" s="5"/>
-      <c r="AQ41" s="5"/>
-      <c r="AR41" s="5"/>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
+      <c r="AF41" s="17"/>
+      <c r="AG41" s="17"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="17"/>
+      <c r="AJ41" s="17"/>
+      <c r="AK41" s="17"/>
+      <c r="AL41" s="17"/>
+      <c r="AM41" s="17"/>
+      <c r="AN41" s="17"/>
+      <c r="AO41" s="17"/>
+      <c r="AP41" s="17"/>
+      <c r="AQ41" s="17"/>
+      <c r="AR41" s="17"/>
+      <c r="AS41" s="17"/>
+      <c r="AT41" s="17"/>
       <c r="AU41" s="5"/>
-    </row>
-    <row r="42" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+      <c r="AV41" s="19"/>
+      <c r="AW41" s="19"/>
+    </row>
+    <row r="42" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>23</v>
       </c>
@@ -5596,89 +5730,223 @@
       <c r="AS42" s="14"/>
       <c r="AT42" s="14"/>
       <c r="AU42" s="14"/>
-    </row>
-    <row r="43" spans="1:47" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="3"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
-      <c r="AD43" s="3"/>
-      <c r="AE43" s="3"/>
-      <c r="AF43" s="3"/>
-      <c r="AG43" s="3"/>
-      <c r="AH43" s="3"/>
-      <c r="AI43" s="3"/>
-      <c r="AJ43" s="3"/>
-      <c r="AK43" s="3"/>
-      <c r="AL43" s="3"/>
-      <c r="AM43" s="3"/>
-      <c r="AN43" s="3"/>
-      <c r="AO43" s="3"/>
-      <c r="AP43" s="3"/>
-      <c r="AQ43" s="3"/>
-      <c r="AR43" s="3"/>
-      <c r="AS43" s="3"/>
-      <c r="AT43" s="3"/>
-      <c r="AU43" s="3"/>
-    </row>
-    <row r="44" spans="1:47" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="3"/>
-      <c r="AB44" s="3"/>
-      <c r="AC44" s="3"/>
-      <c r="AD44" s="3"/>
-      <c r="AE44" s="3"/>
-      <c r="AF44" s="3"/>
-      <c r="AG44" s="3"/>
-      <c r="AH44" s="3"/>
-      <c r="AI44" s="3"/>
-      <c r="AJ44" s="3"/>
-      <c r="AK44" s="3"/>
-      <c r="AL44" s="3"/>
-      <c r="AM44" s="3"/>
-      <c r="AN44" s="3"/>
-      <c r="AO44" s="3"/>
-      <c r="AP44" s="3"/>
-      <c r="AQ44" s="3"/>
-      <c r="AR44" s="3"/>
-      <c r="AS44" s="3"/>
-      <c r="AT44" s="3"/>
-      <c r="AU44" s="3"/>
-    </row>
-    <row r="45" spans="1:47" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="3"/>
-      <c r="AB45" s="3"/>
-      <c r="AC45" s="3"/>
-      <c r="AD45" s="3"/>
-      <c r="AE45" s="3"/>
-      <c r="AF45" s="3"/>
-      <c r="AG45" s="3"/>
-      <c r="AH45" s="3"/>
-      <c r="AI45" s="3"/>
-      <c r="AJ45" s="3"/>
-      <c r="AK45" s="3"/>
-      <c r="AL45" s="3"/>
-      <c r="AM45" s="3"/>
-      <c r="AN45" s="3"/>
-      <c r="AO45" s="3"/>
-      <c r="AP45" s="3"/>
-      <c r="AQ45" s="3"/>
-      <c r="AR45" s="3"/>
-      <c r="AS45" s="3"/>
-      <c r="AT45" s="3"/>
-      <c r="AU45" s="3"/>
-    </row>
-    <row r="46" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+      <c r="AV42" s="19"/>
+      <c r="AW42" s="19"/>
+    </row>
+    <row r="43" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G43" s="18">
+        <v>2.9730698151640085</v>
+      </c>
+      <c r="H43" s="18">
+        <v>1.4248241684604661</v>
+      </c>
+      <c r="I43" s="18">
+        <v>0.63649605682587007</v>
+      </c>
+      <c r="J43" s="18">
+        <v>0.55398989123991582</v>
+      </c>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18">
+        <v>0.12599215393378366</v>
+      </c>
+      <c r="R43" s="18">
+        <v>0.16989442556435064</v>
+      </c>
+      <c r="S43" s="18">
+        <v>0.11802276508069921</v>
+      </c>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="14"/>
+      <c r="AE43" s="14"/>
+      <c r="AF43" s="14"/>
+      <c r="AG43" s="14"/>
+      <c r="AH43" s="14"/>
+      <c r="AI43" s="14"/>
+      <c r="AJ43" s="14"/>
+      <c r="AK43" s="14"/>
+      <c r="AL43" s="14"/>
+      <c r="AM43" s="14"/>
+      <c r="AN43" s="14"/>
+      <c r="AO43" s="14"/>
+      <c r="AP43" s="14"/>
+      <c r="AQ43" s="14"/>
+      <c r="AR43" s="14"/>
+      <c r="AS43" s="14"/>
+      <c r="AT43" s="14"/>
+      <c r="AU43" s="14"/>
+      <c r="AV43" s="19"/>
+      <c r="AW43" s="19"/>
+    </row>
+    <row r="44" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G44" s="18">
+        <v>6.3728715019088673</v>
+      </c>
+      <c r="H44" s="18">
+        <v>4.0166491027743199</v>
+      </c>
+      <c r="I44" s="18">
+        <v>2.7392063590680351</v>
+      </c>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18">
+        <v>2.3911562386477527</v>
+      </c>
+      <c r="L44" s="18">
+        <v>0.86800207743045099</v>
+      </c>
+      <c r="M44" s="18">
+        <v>10.652301255507242</v>
+      </c>
+      <c r="N44" s="18">
+        <v>0.69577929827700402</v>
+      </c>
+      <c r="O44" s="18">
+        <v>0.62273120332780196</v>
+      </c>
+      <c r="P44" s="18">
+        <v>5.2912403056869145E-2</v>
+      </c>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="18"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="14"/>
+      <c r="AE44" s="14"/>
+      <c r="AF44" s="14"/>
+      <c r="AG44" s="14"/>
+      <c r="AH44" s="14"/>
+      <c r="AI44" s="14"/>
+      <c r="AJ44" s="14"/>
+      <c r="AK44" s="14"/>
+      <c r="AL44" s="14"/>
+      <c r="AM44" s="14"/>
+      <c r="AN44" s="14"/>
+      <c r="AO44" s="14"/>
+      <c r="AP44" s="14"/>
+      <c r="AQ44" s="14"/>
+      <c r="AR44" s="14"/>
+      <c r="AS44" s="14"/>
+      <c r="AT44" s="14"/>
+      <c r="AU44" s="14"/>
+      <c r="AV44" s="19"/>
+      <c r="AW44" s="19"/>
+    </row>
+    <row r="45" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G45" s="18">
+        <v>1.9851627680153705</v>
+      </c>
+      <c r="H45" s="18">
+        <v>1.6878884519265402</v>
+      </c>
+      <c r="I45" s="18">
+        <v>1.096917058518756</v>
+      </c>
+      <c r="J45" s="18">
+        <v>0.34077551427312103</v>
+      </c>
+      <c r="K45" s="18">
+        <v>0.28755842070894655</v>
+      </c>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18">
+        <v>0.29038008437232177</v>
+      </c>
+      <c r="O45" s="18">
+        <v>6.6092028490439061E-2</v>
+      </c>
+      <c r="P45" s="18">
+        <v>1.9793577480628551E-2</v>
+      </c>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="14"/>
+      <c r="AC45" s="14"/>
+      <c r="AD45" s="14"/>
+      <c r="AE45" s="14"/>
+      <c r="AF45" s="14"/>
+      <c r="AG45" s="14"/>
+      <c r="AH45" s="14"/>
+      <c r="AI45" s="14"/>
+      <c r="AJ45" s="14"/>
+      <c r="AK45" s="14"/>
+      <c r="AL45" s="14"/>
+      <c r="AM45" s="14"/>
+      <c r="AN45" s="14"/>
+      <c r="AO45" s="14"/>
+      <c r="AP45" s="14"/>
+      <c r="AQ45" s="14"/>
+      <c r="AR45" s="14"/>
+      <c r="AS45" s="14"/>
+      <c r="AT45" s="14"/>
+      <c r="AU45" s="14"/>
+      <c r="AV45" s="19"/>
+      <c r="AW45" s="19"/>
+    </row>
+    <row r="46" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5705,7 +5973,7 @@
       <c r="AT46" s="3"/>
       <c r="AU46" s="3"/>
     </row>
-    <row r="47" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5732,7 +6000,7 @@
       <c r="AT47" s="3"/>
       <c r="AU47" s="3"/>
     </row>
-    <row r="48" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5759,7 +6027,7 @@
       <c r="AT48" s="3"/>
       <c r="AU48" s="3"/>
     </row>
-    <row r="49" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5786,7 +6054,7 @@
       <c r="AT49" s="3"/>
       <c r="AU49" s="3"/>
     </row>
-    <row r="50" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5813,7 +6081,7 @@
       <c r="AT50" s="3"/>
       <c r="AU50" s="3"/>
     </row>
-    <row r="51" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5840,7 +6108,7 @@
       <c r="AT51" s="3"/>
       <c r="AU51" s="3"/>
     </row>
-    <row r="52" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5867,7 +6135,7 @@
       <c r="AT52" s="3"/>
       <c r="AU52" s="3"/>
     </row>
-    <row r="53" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5894,7 +6162,7 @@
       <c r="AT53" s="3"/>
       <c r="AU53" s="3"/>
     </row>
-    <row r="54" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5921,7 +6189,7 @@
       <c r="AT54" s="3"/>
       <c r="AU54" s="3"/>
     </row>
-    <row r="55" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -5948,7 +6216,7 @@
       <c r="AT55" s="3"/>
       <c r="AU55" s="3"/>
     </row>
-    <row r="56" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -5975,7 +6243,7 @@
       <c r="AT56" s="3"/>
       <c r="AU56" s="3"/>
     </row>
-    <row r="57" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -6002,7 +6270,7 @@
       <c r="AT57" s="3"/>
       <c r="AU57" s="3"/>
     </row>
-    <row r="58" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -6029,7 +6297,7 @@
       <c r="AT58" s="3"/>
       <c r="AU58" s="3"/>
     </row>
-    <row r="59" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -6056,7 +6324,7 @@
       <c r="AT59" s="3"/>
       <c r="AU59" s="3"/>
     </row>
-    <row r="60" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -6083,7 +6351,7 @@
       <c r="AT60" s="3"/>
       <c r="AU60" s="3"/>
     </row>
-    <row r="61" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -6110,7 +6378,7 @@
       <c r="AT61" s="3"/>
       <c r="AU61" s="3"/>
     </row>
-    <row r="62" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -6137,7 +6405,7 @@
       <c r="AT62" s="3"/>
       <c r="AU62" s="3"/>
     </row>
-    <row r="63" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -6164,7 +6432,7 @@
       <c r="AT63" s="3"/>
       <c r="AU63" s="3"/>
     </row>
-    <row r="64" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -6191,7 +6459,7 @@
       <c r="AT64" s="3"/>
       <c r="AU64" s="3"/>
     </row>
-    <row r="65" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -6218,7 +6486,7 @@
       <c r="AT65" s="3"/>
       <c r="AU65" s="3"/>
     </row>
-    <row r="66" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -6245,7 +6513,7 @@
       <c r="AT66" s="3"/>
       <c r="AU66" s="3"/>
     </row>
-    <row r="67" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -6272,7 +6540,7 @@
       <c r="AT67" s="3"/>
       <c r="AU67" s="3"/>
     </row>
-    <row r="68" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -6299,7 +6567,7 @@
       <c r="AT68" s="3"/>
       <c r="AU68" s="3"/>
     </row>
-    <row r="69" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -6326,7 +6594,7 @@
       <c r="AT69" s="3"/>
       <c r="AU69" s="3"/>
     </row>
-    <row r="70" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -6353,7 +6621,7 @@
       <c r="AT70" s="3"/>
       <c r="AU70" s="3"/>
     </row>
-    <row r="71" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -6380,7 +6648,7 @@
       <c r="AT71" s="3"/>
       <c r="AU71" s="3"/>
     </row>
-    <row r="72" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -6407,7 +6675,7 @@
       <c r="AT72" s="3"/>
       <c r="AU72" s="3"/>
     </row>
-    <row r="73" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -6434,7 +6702,7 @@
       <c r="AT73" s="3"/>
       <c r="AU73" s="3"/>
     </row>
-    <row r="74" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -6461,7 +6729,7 @@
       <c r="AT74" s="3"/>
       <c r="AU74" s="3"/>
     </row>
-    <row r="75" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -6488,7 +6756,7 @@
       <c r="AT75" s="3"/>
       <c r="AU75" s="3"/>
     </row>
-    <row r="76" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -6515,7 +6783,7 @@
       <c r="AT76" s="3"/>
       <c r="AU76" s="3"/>
     </row>
-    <row r="77" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -6542,7 +6810,7 @@
       <c r="AT77" s="3"/>
       <c r="AU77" s="3"/>
     </row>
-    <row r="78" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -6569,7 +6837,7 @@
       <c r="AT78" s="3"/>
       <c r="AU78" s="3"/>
     </row>
-    <row r="79" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -6596,7 +6864,7 @@
       <c r="AT79" s="3"/>
       <c r="AU79" s="3"/>
     </row>
-    <row r="80" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -6623,7 +6891,7 @@
       <c r="AT80" s="3"/>
       <c r="AU80" s="3"/>
     </row>
-    <row r="81" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -6650,7 +6918,7 @@
       <c r="AT81" s="3"/>
       <c r="AU81" s="3"/>
     </row>
-    <row r="82" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -6677,7 +6945,7 @@
       <c r="AT82" s="3"/>
       <c r="AU82" s="3"/>
     </row>
-    <row r="83" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -6704,7 +6972,7 @@
       <c r="AT83" s="3"/>
       <c r="AU83" s="3"/>
     </row>
-    <row r="84" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -6731,7 +6999,7 @@
       <c r="AT84" s="3"/>
       <c r="AU84" s="3"/>
     </row>
-    <row r="85" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -6758,7 +7026,7 @@
       <c r="AT85" s="3"/>
       <c r="AU85" s="3"/>
     </row>
-    <row r="86" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -6785,7 +7053,7 @@
       <c r="AT86" s="3"/>
       <c r="AU86" s="3"/>
     </row>
-    <row r="87" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -6812,7 +7080,7 @@
       <c r="AT87" s="3"/>
       <c r="AU87" s="3"/>
     </row>
-    <row r="88" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -6839,7 +7107,7 @@
       <c r="AT88" s="3"/>
       <c r="AU88" s="3"/>
     </row>
-    <row r="89" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -6866,7 +7134,7 @@
       <c r="AT89" s="3"/>
       <c r="AU89" s="3"/>
     </row>
-    <row r="90" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -6893,7 +7161,7 @@
       <c r="AT90" s="3"/>
       <c r="AU90" s="3"/>
     </row>
-    <row r="91" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -6920,7 +7188,7 @@
       <c r="AT91" s="3"/>
       <c r="AU91" s="3"/>
     </row>
-    <row r="92" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -6947,7 +7215,7 @@
       <c r="AT92" s="3"/>
       <c r="AU92" s="3"/>
     </row>
-    <row r="93" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -6974,7 +7242,7 @@
       <c r="AT93" s="3"/>
       <c r="AU93" s="3"/>
     </row>
-    <row r="94" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -7001,7 +7269,7 @@
       <c r="AT94" s="3"/>
       <c r="AU94" s="3"/>
     </row>
-    <row r="95" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -7028,7 +7296,7 @@
       <c r="AT95" s="3"/>
       <c r="AU95" s="3"/>
     </row>
-    <row r="96" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -7055,7 +7323,7 @@
       <c r="AT96" s="3"/>
       <c r="AU96" s="3"/>
     </row>
-    <row r="97" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -7082,7 +7350,7 @@
       <c r="AT97" s="3"/>
       <c r="AU97" s="3"/>
     </row>
-    <row r="98" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -7109,7 +7377,7 @@
       <c r="AT98" s="3"/>
       <c r="AU98" s="3"/>
     </row>
-    <row r="99" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -7136,7 +7404,7 @@
       <c r="AT99" s="3"/>
       <c r="AU99" s="3"/>
     </row>
-    <row r="100" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -7163,7 +7431,7 @@
       <c r="AT100" s="3"/>
       <c r="AU100" s="3"/>
     </row>
-    <row r="101" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -7190,7 +7458,7 @@
       <c r="AT101" s="3"/>
       <c r="AU101" s="3"/>
     </row>
-    <row r="102" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -7217,7 +7485,7 @@
       <c r="AT102" s="3"/>
       <c r="AU102" s="3"/>
     </row>
-    <row r="103" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -7244,7 +7512,7 @@
       <c r="AT103" s="3"/>
       <c r="AU103" s="3"/>
     </row>
-    <row r="104" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -7271,7 +7539,7 @@
       <c r="AT104" s="3"/>
       <c r="AU104" s="3"/>
     </row>
-    <row r="105" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -7298,7 +7566,7 @@
       <c r="AT105" s="3"/>
       <c r="AU105" s="3"/>
     </row>
-    <row r="106" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -7325,7 +7593,7 @@
       <c r="AT106" s="3"/>
       <c r="AU106" s="3"/>
     </row>
-    <row r="107" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -7352,7 +7620,7 @@
       <c r="AT107" s="3"/>
       <c r="AU107" s="3"/>
     </row>
-    <row r="108" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -7379,7 +7647,7 @@
       <c r="AT108" s="3"/>
       <c r="AU108" s="3"/>
     </row>
-    <row r="109" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -7406,7 +7674,7 @@
       <c r="AT109" s="3"/>
       <c r="AU109" s="3"/>
     </row>
-    <row r="110" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -7433,7 +7701,7 @@
       <c r="AT110" s="3"/>
       <c r="AU110" s="3"/>
     </row>
-    <row r="111" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -7460,7 +7728,7 @@
       <c r="AT111" s="3"/>
       <c r="AU111" s="3"/>
     </row>
-    <row r="112" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -7487,7 +7755,7 @@
       <c r="AT112" s="3"/>
       <c r="AU112" s="3"/>
     </row>
-    <row r="113" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -7514,7 +7782,7 @@
       <c r="AT113" s="3"/>
       <c r="AU113" s="3"/>
     </row>
-    <row r="114" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -7541,7 +7809,7 @@
       <c r="AT114" s="3"/>
       <c r="AU114" s="3"/>
     </row>
-    <row r="115" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -7568,7 +7836,7 @@
       <c r="AT115" s="3"/>
       <c r="AU115" s="3"/>
     </row>
-    <row r="116" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -7595,7 +7863,7 @@
       <c r="AT116" s="3"/>
       <c r="AU116" s="3"/>
     </row>
-    <row r="117" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -7622,7 +7890,7 @@
       <c r="AT117" s="3"/>
       <c r="AU117" s="3"/>
     </row>
-    <row r="118" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -7649,7 +7917,7 @@
       <c r="AT118" s="3"/>
       <c r="AU118" s="3"/>
     </row>
-    <row r="119" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -7676,7 +7944,7 @@
       <c r="AT119" s="3"/>
       <c r="AU119" s="3"/>
     </row>
-    <row r="120" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -7703,7 +7971,7 @@
       <c r="AT120" s="3"/>
       <c r="AU120" s="3"/>
     </row>
-    <row r="121" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -7730,7 +7998,7 @@
       <c r="AT121" s="3"/>
       <c r="AU121" s="3"/>
     </row>
-    <row r="122" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -7757,7 +8025,7 @@
       <c r="AT122" s="3"/>
       <c r="AU122" s="3"/>
     </row>
-    <row r="123" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -7784,7 +8052,7 @@
       <c r="AT123" s="3"/>
       <c r="AU123" s="3"/>
     </row>
-    <row r="124" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -7811,7 +8079,7 @@
       <c r="AT124" s="3"/>
       <c r="AU124" s="3"/>
     </row>
-    <row r="125" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -7838,7 +8106,7 @@
       <c r="AT125" s="3"/>
       <c r="AU125" s="3"/>
     </row>
-    <row r="126" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -7865,7 +8133,7 @@
       <c r="AT126" s="3"/>
       <c r="AU126" s="3"/>
     </row>
-    <row r="127" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -7892,7 +8160,7 @@
       <c r="AT127" s="3"/>
       <c r="AU127" s="3"/>
     </row>
-    <row r="128" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -7919,7 +8187,7 @@
       <c r="AT128" s="3"/>
       <c r="AU128" s="3"/>
     </row>
-    <row r="129" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -7946,7 +8214,7 @@
       <c r="AT129" s="3"/>
       <c r="AU129" s="3"/>
     </row>
-    <row r="130" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -7973,7 +8241,7 @@
       <c r="AT130" s="3"/>
       <c r="AU130" s="3"/>
     </row>
-    <row r="131" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -8000,7 +8268,7 @@
       <c r="AT131" s="3"/>
       <c r="AU131" s="3"/>
     </row>
-    <row r="132" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -8027,7 +8295,7 @@
       <c r="AT132" s="3"/>
       <c r="AU132" s="3"/>
     </row>
-    <row r="133" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -8054,7 +8322,7 @@
       <c r="AT133" s="3"/>
       <c r="AU133" s="3"/>
     </row>
-    <row r="134" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -8081,7 +8349,7 @@
       <c r="AT134" s="3"/>
       <c r="AU134" s="3"/>
     </row>
-    <row r="135" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -8108,7 +8376,7 @@
       <c r="AT135" s="3"/>
       <c r="AU135" s="3"/>
     </row>
-    <row r="136" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -8135,7 +8403,7 @@
       <c r="AT136" s="3"/>
       <c r="AU136" s="3"/>
     </row>
-    <row r="137" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -8162,7 +8430,7 @@
       <c r="AT137" s="3"/>
       <c r="AU137" s="3"/>
     </row>
-    <row r="138" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -8189,7 +8457,7 @@
       <c r="AT138" s="3"/>
       <c r="AU138" s="3"/>
     </row>
-    <row r="139" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -8216,7 +8484,7 @@
       <c r="AT139" s="3"/>
       <c r="AU139" s="3"/>
     </row>
-    <row r="140" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -8243,7 +8511,7 @@
       <c r="AT140" s="3"/>
       <c r="AU140" s="3"/>
     </row>
-    <row r="141" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -8270,7 +8538,7 @@
       <c r="AT141" s="3"/>
       <c r="AU141" s="3"/>
     </row>
-    <row r="142" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -8297,7 +8565,7 @@
       <c r="AT142" s="3"/>
       <c r="AU142" s="3"/>
     </row>
-    <row r="143" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -8324,7 +8592,7 @@
       <c r="AT143" s="3"/>
       <c r="AU143" s="3"/>
     </row>
-    <row r="144" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -8351,7 +8619,7 @@
       <c r="AT144" s="3"/>
       <c r="AU144" s="3"/>
     </row>
-    <row r="145" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -8378,7 +8646,7 @@
       <c r="AT145" s="3"/>
       <c r="AU145" s="3"/>
     </row>
-    <row r="146" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -8405,7 +8673,7 @@
       <c r="AT146" s="3"/>
       <c r="AU146" s="3"/>
     </row>
-    <row r="147" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -8432,7 +8700,7 @@
       <c r="AT147" s="3"/>
       <c r="AU147" s="3"/>
     </row>
-    <row r="148" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -8459,7 +8727,7 @@
       <c r="AT148" s="3"/>
       <c r="AU148" s="3"/>
     </row>
-    <row r="149" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -8486,7 +8754,7 @@
       <c r="AT149" s="3"/>
       <c r="AU149" s="3"/>
     </row>
-    <row r="150" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -8513,7 +8781,7 @@
       <c r="AT150" s="3"/>
       <c r="AU150" s="3"/>
     </row>
-    <row r="151" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -8540,7 +8808,7 @@
       <c r="AT151" s="3"/>
       <c r="AU151" s="3"/>
     </row>
-    <row r="152" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -8567,7 +8835,7 @@
       <c r="AT152" s="3"/>
       <c r="AU152" s="3"/>
     </row>
-    <row r="153" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -8594,7 +8862,7 @@
       <c r="AT153" s="3"/>
       <c r="AU153" s="3"/>
     </row>
-    <row r="154" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -8621,7 +8889,7 @@
       <c r="AT154" s="3"/>
       <c r="AU154" s="3"/>
     </row>
-    <row r="155" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -8648,7 +8916,7 @@
       <c r="AT155" s="3"/>
       <c r="AU155" s="3"/>
     </row>
-    <row r="156" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -8675,7 +8943,7 @@
       <c r="AT156" s="3"/>
       <c r="AU156" s="3"/>
     </row>
-    <row r="157" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -8702,7 +8970,7 @@
       <c r="AT157" s="3"/>
       <c r="AU157" s="3"/>
     </row>
-    <row r="158" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -8729,7 +8997,7 @@
       <c r="AT158" s="3"/>
       <c r="AU158" s="3"/>
     </row>
-    <row r="159" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -8756,7 +9024,7 @@
       <c r="AT159" s="3"/>
       <c r="AU159" s="3"/>
     </row>
-    <row r="160" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -8783,7 +9051,7 @@
       <c r="AT160" s="3"/>
       <c r="AU160" s="3"/>
     </row>
-    <row r="161" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -8810,7 +9078,7 @@
       <c r="AT161" s="3"/>
       <c r="AU161" s="3"/>
     </row>
-    <row r="162" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -8837,7 +9105,7 @@
       <c r="AT162" s="3"/>
       <c r="AU162" s="3"/>
     </row>
-    <row r="163" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -8864,7 +9132,7 @@
       <c r="AT163" s="3"/>
       <c r="AU163" s="3"/>
     </row>
-    <row r="164" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -8891,7 +9159,7 @@
       <c r="AT164" s="3"/>
       <c r="AU164" s="3"/>
     </row>
-    <row r="165" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -8918,7 +9186,7 @@
       <c r="AT165" s="3"/>
       <c r="AU165" s="3"/>
     </row>
-    <row r="166" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -8945,7 +9213,7 @@
       <c r="AT166" s="3"/>
       <c r="AU166" s="3"/>
     </row>
-    <row r="167" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -8972,7 +9240,7 @@
       <c r="AT167" s="3"/>
       <c r="AU167" s="3"/>
     </row>
-    <row r="168" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -8999,7 +9267,7 @@
       <c r="AT168" s="3"/>
       <c r="AU168" s="3"/>
     </row>
-    <row r="169" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -9026,7 +9294,7 @@
       <c r="AT169" s="3"/>
       <c r="AU169" s="3"/>
     </row>
-    <row r="170" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -9053,7 +9321,7 @@
       <c r="AT170" s="3"/>
       <c r="AU170" s="3"/>
     </row>
-    <row r="171" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -9080,7 +9348,7 @@
       <c r="AT171" s="3"/>
       <c r="AU171" s="3"/>
     </row>
-    <row r="172" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -9107,7 +9375,7 @@
       <c r="AT172" s="3"/>
       <c r="AU172" s="3"/>
     </row>
-    <row r="173" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -9134,7 +9402,7 @@
       <c r="AT173" s="3"/>
       <c r="AU173" s="3"/>
     </row>
-    <row r="174" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -9161,7 +9429,7 @@
       <c r="AT174" s="3"/>
       <c r="AU174" s="3"/>
     </row>
-    <row r="175" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -9188,7 +9456,7 @@
       <c r="AT175" s="3"/>
       <c r="AU175" s="3"/>
     </row>
-    <row r="176" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -9215,7 +9483,7 @@
       <c r="AT176" s="3"/>
       <c r="AU176" s="3"/>
     </row>
-    <row r="177" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -9242,7 +9510,7 @@
       <c r="AT177" s="3"/>
       <c r="AU177" s="3"/>
     </row>
-    <row r="178" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -9269,7 +9537,7 @@
       <c r="AT178" s="3"/>
       <c r="AU178" s="3"/>
     </row>
-    <row r="179" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -9296,7 +9564,7 @@
       <c r="AT179" s="3"/>
       <c r="AU179" s="3"/>
     </row>
-    <row r="180" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -9323,7 +9591,7 @@
       <c r="AT180" s="3"/>
       <c r="AU180" s="3"/>
     </row>
-    <row r="181" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -9350,7 +9618,7 @@
       <c r="AT181" s="3"/>
       <c r="AU181" s="3"/>
     </row>
-    <row r="182" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -9377,7 +9645,7 @@
       <c r="AT182" s="3"/>
       <c r="AU182" s="3"/>
     </row>
-    <row r="183" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -9404,7 +9672,7 @@
       <c r="AT183" s="3"/>
       <c r="AU183" s="3"/>
     </row>
-    <row r="184" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -9431,7 +9699,7 @@
       <c r="AT184" s="3"/>
       <c r="AU184" s="3"/>
     </row>
-    <row r="185" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -9458,7 +9726,7 @@
       <c r="AT185" s="3"/>
       <c r="AU185" s="3"/>
     </row>
-    <row r="186" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -9485,7 +9753,7 @@
       <c r="AT186" s="3"/>
       <c r="AU186" s="3"/>
     </row>
-    <row r="187" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -9512,7 +9780,7 @@
       <c r="AT187" s="3"/>
       <c r="AU187" s="3"/>
     </row>
-    <row r="188" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -9539,7 +9807,7 @@
       <c r="AT188" s="3"/>
       <c r="AU188" s="3"/>
     </row>
-    <row r="189" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -9566,7 +9834,7 @@
       <c r="AT189" s="3"/>
       <c r="AU189" s="3"/>
     </row>
-    <row r="190" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -9593,7 +9861,7 @@
       <c r="AT190" s="3"/>
       <c r="AU190" s="3"/>
     </row>
-    <row r="191" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -9620,7 +9888,7 @@
       <c r="AT191" s="3"/>
       <c r="AU191" s="3"/>
     </row>
-    <row r="192" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -9647,7 +9915,7 @@
       <c r="AT192" s="3"/>
       <c r="AU192" s="3"/>
     </row>
-    <row r="193" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -9674,7 +9942,7 @@
       <c r="AT193" s="3"/>
       <c r="AU193" s="3"/>
     </row>
-    <row r="194" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -9701,7 +9969,7 @@
       <c r="AT194" s="3"/>
       <c r="AU194" s="3"/>
     </row>
-    <row r="195" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -9728,7 +9996,7 @@
       <c r="AT195" s="3"/>
       <c r="AU195" s="3"/>
     </row>
-    <row r="196" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -9755,7 +10023,7 @@
       <c r="AT196" s="3"/>
       <c r="AU196" s="3"/>
     </row>
-    <row r="197" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -9782,7 +10050,7 @@
       <c r="AT197" s="3"/>
       <c r="AU197" s="3"/>
     </row>
-    <row r="198" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -9809,7 +10077,7 @@
       <c r="AT198" s="3"/>
       <c r="AU198" s="3"/>
     </row>
-    <row r="199" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -9836,7 +10104,7 @@
       <c r="AT199" s="3"/>
       <c r="AU199" s="3"/>
     </row>
-    <row r="200" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -9863,7 +10131,7 @@
       <c r="AT200" s="3"/>
       <c r="AU200" s="3"/>
     </row>
-    <row r="201" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -9890,7 +10158,7 @@
       <c r="AT201" s="3"/>
       <c r="AU201" s="3"/>
     </row>
-    <row r="202" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -9917,7 +10185,7 @@
       <c r="AT202" s="3"/>
       <c r="AU202" s="3"/>
     </row>
-    <row r="203" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -9944,7 +10212,7 @@
       <c r="AT203" s="3"/>
       <c r="AU203" s="3"/>
     </row>
-    <row r="204" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -9971,7 +10239,7 @@
       <c r="AT204" s="3"/>
       <c r="AU204" s="3"/>
     </row>
-    <row r="205" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -9998,7 +10266,7 @@
       <c r="AT205" s="3"/>
       <c r="AU205" s="3"/>
     </row>
-    <row r="206" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -10025,7 +10293,7 @@
       <c r="AT206" s="3"/>
       <c r="AU206" s="3"/>
     </row>
-    <row r="207" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -10052,7 +10320,7 @@
       <c r="AT207" s="3"/>
       <c r="AU207" s="3"/>
     </row>
-    <row r="208" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -10079,7 +10347,7 @@
       <c r="AT208" s="3"/>
       <c r="AU208" s="3"/>
     </row>
-    <row r="209" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -10106,7 +10374,7 @@
       <c r="AT209" s="3"/>
       <c r="AU209" s="3"/>
     </row>
-    <row r="210" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -10133,7 +10401,7 @@
       <c r="AT210" s="3"/>
       <c r="AU210" s="3"/>
     </row>
-    <row r="211" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -10160,7 +10428,7 @@
       <c r="AT211" s="3"/>
       <c r="AU211" s="3"/>
     </row>
-    <row r="212" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -10187,7 +10455,7 @@
       <c r="AT212" s="3"/>
       <c r="AU212" s="3"/>
     </row>
-    <row r="213" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -10214,7 +10482,7 @@
       <c r="AT213" s="3"/>
       <c r="AU213" s="3"/>
     </row>
-    <row r="214" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -10241,7 +10509,7 @@
       <c r="AT214" s="3"/>
       <c r="AU214" s="3"/>
     </row>
-    <row r="215" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -10268,7 +10536,7 @@
       <c r="AT215" s="3"/>
       <c r="AU215" s="3"/>
     </row>
-    <row r="216" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -10295,7 +10563,7 @@
       <c r="AT216" s="3"/>
       <c r="AU216" s="3"/>
     </row>
-    <row r="217" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -10322,7 +10590,7 @@
       <c r="AT217" s="3"/>
       <c r="AU217" s="3"/>
     </row>
-    <row r="218" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -10349,7 +10617,7 @@
       <c r="AT218" s="3"/>
       <c r="AU218" s="3"/>
     </row>
-    <row r="219" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -10376,7 +10644,7 @@
       <c r="AT219" s="3"/>
       <c r="AU219" s="3"/>
     </row>
-    <row r="220" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -10403,7 +10671,7 @@
       <c r="AT220" s="3"/>
       <c r="AU220" s="3"/>
     </row>
-    <row r="221" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -10430,7 +10698,7 @@
       <c r="AT221" s="3"/>
       <c r="AU221" s="3"/>
     </row>
-    <row r="222" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -10457,7 +10725,7 @@
       <c r="AT222" s="3"/>
       <c r="AU222" s="3"/>
     </row>
-    <row r="223" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -10484,7 +10752,7 @@
       <c r="AT223" s="3"/>
       <c r="AU223" s="3"/>
     </row>
-    <row r="224" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -10511,7 +10779,7 @@
       <c r="AT224" s="3"/>
       <c r="AU224" s="3"/>
     </row>
-    <row r="225" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -10538,7 +10806,7 @@
       <c r="AT225" s="3"/>
       <c r="AU225" s="3"/>
     </row>
-    <row r="226" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -10565,7 +10833,7 @@
       <c r="AT226" s="3"/>
       <c r="AU226" s="3"/>
     </row>
-    <row r="227" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -10592,7 +10860,7 @@
       <c r="AT227" s="3"/>
       <c r="AU227" s="3"/>
     </row>
-    <row r="228" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -10619,7 +10887,7 @@
       <c r="AT228" s="3"/>
       <c r="AU228" s="3"/>
     </row>
-    <row r="229" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -10646,7 +10914,7 @@
       <c r="AT229" s="3"/>
       <c r="AU229" s="3"/>
     </row>
-    <row r="230" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -10673,7 +10941,7 @@
       <c r="AT230" s="3"/>
       <c r="AU230" s="3"/>
     </row>
-    <row r="231" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -10700,7 +10968,7 @@
       <c r="AT231" s="3"/>
       <c r="AU231" s="3"/>
     </row>
-    <row r="232" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -10727,7 +10995,7 @@
       <c r="AT232" s="3"/>
       <c r="AU232" s="3"/>
     </row>
-    <row r="233" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -10754,7 +11022,7 @@
       <c r="AT233" s="3"/>
       <c r="AU233" s="3"/>
     </row>
-    <row r="234" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -10781,7 +11049,7 @@
       <c r="AT234" s="3"/>
       <c r="AU234" s="3"/>
     </row>
-    <row r="235" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -10808,7 +11076,7 @@
       <c r="AT235" s="3"/>
       <c r="AU235" s="3"/>
     </row>
-    <row r="236" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -10835,7 +11103,7 @@
       <c r="AT236" s="3"/>
       <c r="AU236" s="3"/>
     </row>
-    <row r="237" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -10862,7 +11130,7 @@
       <c r="AT237" s="3"/>
       <c r="AU237" s="3"/>
     </row>
-    <row r="238" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -10889,7 +11157,7 @@
       <c r="AT238" s="3"/>
       <c r="AU238" s="3"/>
     </row>
-    <row r="239" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -10916,7 +11184,7 @@
       <c r="AT239" s="3"/>
       <c r="AU239" s="3"/>
     </row>
-    <row r="240" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -10943,7 +11211,7 @@
       <c r="AT240" s="3"/>
       <c r="AU240" s="3"/>
     </row>
-    <row r="241" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -10970,7 +11238,7 @@
       <c r="AT241" s="3"/>
       <c r="AU241" s="3"/>
     </row>
-    <row r="242" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -10997,7 +11265,7 @@
       <c r="AT242" s="3"/>
       <c r="AU242" s="3"/>
     </row>
-    <row r="243" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -11024,7 +11292,7 @@
       <c r="AT243" s="3"/>
       <c r="AU243" s="3"/>
     </row>
-    <row r="244" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -11051,7 +11319,7 @@
       <c r="AT244" s="3"/>
       <c r="AU244" s="3"/>
     </row>
-    <row r="245" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -11078,7 +11346,7 @@
       <c r="AT245" s="3"/>
       <c r="AU245" s="3"/>
     </row>
-    <row r="246" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -11105,7 +11373,7 @@
       <c r="AT246" s="3"/>
       <c r="AU246" s="3"/>
     </row>
-    <row r="247" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -11132,7 +11400,7 @@
       <c r="AT247" s="3"/>
       <c r="AU247" s="3"/>
     </row>
-    <row r="248" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -11159,7 +11427,7 @@
       <c r="AT248" s="3"/>
       <c r="AU248" s="3"/>
     </row>
-    <row r="249" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -11186,7 +11454,7 @@
       <c r="AT249" s="3"/>
       <c r="AU249" s="3"/>
     </row>
-    <row r="250" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -11213,7 +11481,7 @@
       <c r="AT250" s="3"/>
       <c r="AU250" s="3"/>
     </row>
-    <row r="251" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -11240,7 +11508,7 @@
       <c r="AT251" s="3"/>
       <c r="AU251" s="3"/>
     </row>
-    <row r="252" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -11267,7 +11535,7 @@
       <c r="AT252" s="3"/>
       <c r="AU252" s="3"/>
     </row>
-    <row r="253" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -11294,7 +11562,7 @@
       <c r="AT253" s="3"/>
       <c r="AU253" s="3"/>
     </row>
-    <row r="254" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -11321,7 +11589,7 @@
       <c r="AT254" s="3"/>
       <c r="AU254" s="3"/>
     </row>
-    <row r="255" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -11348,7 +11616,7 @@
       <c r="AT255" s="3"/>
       <c r="AU255" s="3"/>
     </row>
-    <row r="256" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -11375,7 +11643,7 @@
       <c r="AT256" s="3"/>
       <c r="AU256" s="3"/>
     </row>
-    <row r="257" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -11402,7 +11670,7 @@
       <c r="AT257" s="3"/>
       <c r="AU257" s="3"/>
     </row>
-    <row r="258" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -11429,7 +11697,7 @@
       <c r="AT258" s="3"/>
       <c r="AU258" s="3"/>
     </row>
-    <row r="259" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -11456,7 +11724,7 @@
       <c r="AT259" s="3"/>
       <c r="AU259" s="3"/>
     </row>
-    <row r="260" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -11483,7 +11751,7 @@
       <c r="AT260" s="3"/>
       <c r="AU260" s="3"/>
     </row>
-    <row r="261" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -11510,7 +11778,7 @@
       <c r="AT261" s="3"/>
       <c r="AU261" s="3"/>
     </row>
-    <row r="262" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -11537,7 +11805,7 @@
       <c r="AT262" s="3"/>
       <c r="AU262" s="3"/>
     </row>
-    <row r="263" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -11564,7 +11832,7 @@
       <c r="AT263" s="3"/>
       <c r="AU263" s="3"/>
     </row>
-    <row r="264" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -11591,7 +11859,7 @@
       <c r="AT264" s="3"/>
       <c r="AU264" s="3"/>
     </row>
-    <row r="265" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -11618,7 +11886,7 @@
       <c r="AT265" s="3"/>
       <c r="AU265" s="3"/>
     </row>
-    <row r="266" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -11645,7 +11913,7 @@
       <c r="AT266" s="3"/>
       <c r="AU266" s="3"/>
     </row>
-    <row r="267" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -11672,7 +11940,7 @@
       <c r="AT267" s="3"/>
       <c r="AU267" s="3"/>
     </row>
-    <row r="268" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -11699,7 +11967,7 @@
       <c r="AT268" s="3"/>
       <c r="AU268" s="3"/>
     </row>
-    <row r="269" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -11726,7 +11994,7 @@
       <c r="AT269" s="3"/>
       <c r="AU269" s="3"/>
     </row>
-    <row r="270" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -11753,7 +12021,7 @@
       <c r="AT270" s="3"/>
       <c r="AU270" s="3"/>
     </row>
-    <row r="271" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -11780,7 +12048,7 @@
       <c r="AT271" s="3"/>
       <c r="AU271" s="3"/>
     </row>
-    <row r="272" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -11807,7 +12075,7 @@
       <c r="AT272" s="3"/>
       <c r="AU272" s="3"/>
     </row>
-    <row r="273" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -11834,7 +12102,7 @@
       <c r="AT273" s="3"/>
       <c r="AU273" s="3"/>
     </row>
-    <row r="274" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -11861,7 +12129,7 @@
       <c r="AT274" s="3"/>
       <c r="AU274" s="3"/>
     </row>
-    <row r="275" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -11888,7 +12156,7 @@
       <c r="AT275" s="3"/>
       <c r="AU275" s="3"/>
     </row>
-    <row r="276" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -11915,7 +12183,7 @@
       <c r="AT276" s="3"/>
       <c r="AU276" s="3"/>
     </row>
-    <row r="277" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -11942,7 +12210,7 @@
       <c r="AT277" s="3"/>
       <c r="AU277" s="3"/>
     </row>
-    <row r="278" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -11969,7 +12237,7 @@
       <c r="AT278" s="3"/>
       <c r="AU278" s="3"/>
     </row>
-    <row r="279" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -11996,7 +12264,7 @@
       <c r="AT279" s="3"/>
       <c r="AU279" s="3"/>
     </row>
-    <row r="280" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -12023,7 +12291,7 @@
       <c r="AT280" s="3"/>
       <c r="AU280" s="3"/>
     </row>
-    <row r="281" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -12050,7 +12318,7 @@
       <c r="AT281" s="3"/>
       <c r="AU281" s="3"/>
     </row>
-    <row r="282" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -12077,7 +12345,7 @@
       <c r="AT282" s="3"/>
       <c r="AU282" s="3"/>
     </row>
-    <row r="283" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -12104,7 +12372,7 @@
       <c r="AT283" s="3"/>
       <c r="AU283" s="3"/>
     </row>
-    <row r="284" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -12131,7 +12399,7 @@
       <c r="AT284" s="3"/>
       <c r="AU284" s="3"/>
     </row>
-    <row r="285" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -12158,7 +12426,7 @@
       <c r="AT285" s="3"/>
       <c r="AU285" s="3"/>
     </row>
-    <row r="286" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -12185,7 +12453,7 @@
       <c r="AT286" s="3"/>
       <c r="AU286" s="3"/>
     </row>
-    <row r="287" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -12212,7 +12480,7 @@
       <c r="AT287" s="3"/>
       <c r="AU287" s="3"/>
     </row>
-    <row r="288" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -12239,7 +12507,7 @@
       <c r="AT288" s="3"/>
       <c r="AU288" s="3"/>
     </row>
-    <row r="289" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -12266,7 +12534,7 @@
       <c r="AT289" s="3"/>
       <c r="AU289" s="3"/>
     </row>
-    <row r="290" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -12293,7 +12561,7 @@
       <c r="AT290" s="3"/>
       <c r="AU290" s="3"/>
     </row>
-    <row r="291" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -12320,7 +12588,7 @@
       <c r="AT291" s="3"/>
       <c r="AU291" s="3"/>
     </row>
-    <row r="292" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -12347,7 +12615,7 @@
       <c r="AT292" s="3"/>
       <c r="AU292" s="3"/>
     </row>
-    <row r="293" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -12374,7 +12642,7 @@
       <c r="AT293" s="3"/>
       <c r="AU293" s="3"/>
     </row>
-    <row r="294" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -12401,7 +12669,7 @@
       <c r="AT294" s="3"/>
       <c r="AU294" s="3"/>
     </row>
-    <row r="295" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -12428,7 +12696,7 @@
       <c r="AT295" s="3"/>
       <c r="AU295" s="3"/>
     </row>
-    <row r="296" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -12455,7 +12723,7 @@
       <c r="AT296" s="3"/>
       <c r="AU296" s="3"/>
     </row>
-    <row r="297" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -12482,7 +12750,7 @@
       <c r="AT297" s="3"/>
       <c r="AU297" s="3"/>
     </row>
-    <row r="298" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -12509,7 +12777,7 @@
       <c r="AT298" s="3"/>
       <c r="AU298" s="3"/>
     </row>
-    <row r="299" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -12536,7 +12804,7 @@
       <c r="AT299" s="3"/>
       <c r="AU299" s="3"/>
     </row>
-    <row r="300" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -12563,7 +12831,7 @@
       <c r="AT300" s="3"/>
       <c r="AU300" s="3"/>
     </row>
-    <row r="301" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -12590,7 +12858,7 @@
       <c r="AT301" s="3"/>
       <c r="AU301" s="3"/>
     </row>
-    <row r="302" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -12617,7 +12885,7 @@
       <c r="AT302" s="3"/>
       <c r="AU302" s="3"/>
     </row>
-    <row r="303" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -12644,7 +12912,7 @@
       <c r="AT303" s="3"/>
       <c r="AU303" s="3"/>
     </row>
-    <row r="304" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -12671,7 +12939,7 @@
       <c r="AT304" s="3"/>
       <c r="AU304" s="3"/>
     </row>
-    <row r="305" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -12698,7 +12966,7 @@
       <c r="AT305" s="3"/>
       <c r="AU305" s="3"/>
     </row>
-    <row r="306" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -12725,7 +12993,7 @@
       <c r="AT306" s="3"/>
       <c r="AU306" s="3"/>
     </row>
-    <row r="307" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -12752,7 +13020,7 @@
       <c r="AT307" s="3"/>
       <c r="AU307" s="3"/>
     </row>
-    <row r="308" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -12779,7 +13047,7 @@
       <c r="AT308" s="3"/>
       <c r="AU308" s="3"/>
     </row>
-    <row r="309" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -12806,7 +13074,7 @@
       <c r="AT309" s="3"/>
       <c r="AU309" s="3"/>
     </row>
-    <row r="310" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -12833,7 +13101,7 @@
       <c r="AT310" s="3"/>
       <c r="AU310" s="3"/>
     </row>
-    <row r="311" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -12860,7 +13128,7 @@
       <c r="AT311" s="3"/>
       <c r="AU311" s="3"/>
     </row>
-    <row r="312" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -12887,7 +13155,7 @@
       <c r="AT312" s="3"/>
       <c r="AU312" s="3"/>
     </row>
-    <row r="313" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -12914,7 +13182,7 @@
       <c r="AT313" s="3"/>
       <c r="AU313" s="3"/>
     </row>
-    <row r="314" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -12941,7 +13209,7 @@
       <c r="AT314" s="3"/>
       <c r="AU314" s="3"/>
     </row>
-    <row r="315" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -12968,7 +13236,7 @@
       <c r="AT315" s="3"/>
       <c r="AU315" s="3"/>
     </row>
-    <row r="316" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -12995,7 +13263,7 @@
       <c r="AT316" s="3"/>
       <c r="AU316" s="3"/>
     </row>
-    <row r="317" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -13022,7 +13290,7 @@
       <c r="AT317" s="3"/>
       <c r="AU317" s="3"/>
     </row>
-    <row r="318" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -13049,7 +13317,7 @@
       <c r="AT318" s="3"/>
       <c r="AU318" s="3"/>
     </row>
-    <row r="319" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -13076,7 +13344,7 @@
       <c r="AT319" s="3"/>
       <c r="AU319" s="3"/>
     </row>
-    <row r="320" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -13103,7 +13371,7 @@
       <c r="AT320" s="3"/>
       <c r="AU320" s="3"/>
     </row>
-    <row r="321" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -13130,7 +13398,7 @@
       <c r="AT321" s="3"/>
       <c r="AU321" s="3"/>
     </row>
-    <row r="322" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -13157,7 +13425,7 @@
       <c r="AT322" s="3"/>
       <c r="AU322" s="3"/>
     </row>
-    <row r="323" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -13184,7 +13452,7 @@
       <c r="AT323" s="3"/>
       <c r="AU323" s="3"/>
     </row>
-    <row r="324" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -13211,7 +13479,7 @@
       <c r="AT324" s="3"/>
       <c r="AU324" s="3"/>
     </row>
-    <row r="325" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -13238,7 +13506,7 @@
       <c r="AT325" s="3"/>
       <c r="AU325" s="3"/>
     </row>
-    <row r="326" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -13265,7 +13533,7 @@
       <c r="AT326" s="3"/>
       <c r="AU326" s="3"/>
     </row>
-    <row r="327" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -13292,7 +13560,7 @@
       <c r="AT327" s="3"/>
       <c r="AU327" s="3"/>
     </row>
-    <row r="328" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -13319,7 +13587,7 @@
       <c r="AT328" s="3"/>
       <c r="AU328" s="3"/>
     </row>
-    <row r="329" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -13346,7 +13614,7 @@
       <c r="AT329" s="3"/>
       <c r="AU329" s="3"/>
     </row>
-    <row r="330" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -13373,7 +13641,7 @@
       <c r="AT330" s="3"/>
       <c r="AU330" s="3"/>
     </row>
-    <row r="331" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -13400,7 +13668,7 @@
       <c r="AT331" s="3"/>
       <c r="AU331" s="3"/>
     </row>
-    <row r="332" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -13427,7 +13695,7 @@
       <c r="AT332" s="3"/>
       <c r="AU332" s="3"/>
     </row>
-    <row r="333" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -13454,7 +13722,7 @@
       <c r="AT333" s="3"/>
       <c r="AU333" s="3"/>
     </row>
-    <row r="334" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -13481,7 +13749,7 @@
       <c r="AT334" s="3"/>
       <c r="AU334" s="3"/>
     </row>
-    <row r="335" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -13508,7 +13776,7 @@
       <c r="AT335" s="3"/>
       <c r="AU335" s="3"/>
     </row>
-    <row r="336" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -13535,7 +13803,7 @@
       <c r="AT336" s="3"/>
       <c r="AU336" s="3"/>
     </row>
-    <row r="337" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -13562,7 +13830,7 @@
       <c r="AT337" s="3"/>
       <c r="AU337" s="3"/>
     </row>
-    <row r="338" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -13589,7 +13857,7 @@
       <c r="AT338" s="3"/>
       <c r="AU338" s="3"/>
     </row>
-    <row r="339" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -13616,7 +13884,7 @@
       <c r="AT339" s="3"/>
       <c r="AU339" s="3"/>
     </row>
-    <row r="340" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -13643,7 +13911,7 @@
       <c r="AT340" s="3"/>
       <c r="AU340" s="3"/>
     </row>
-    <row r="341" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -13670,7 +13938,7 @@
       <c r="AT341" s="3"/>
       <c r="AU341" s="3"/>
     </row>
-    <row r="342" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -13697,7 +13965,7 @@
       <c r="AT342" s="3"/>
       <c r="AU342" s="3"/>
     </row>
-    <row r="343" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -13724,7 +13992,7 @@
       <c r="AT343" s="3"/>
       <c r="AU343" s="3"/>
     </row>
-    <row r="344" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -13751,7 +14019,7 @@
       <c r="AT344" s="3"/>
       <c r="AU344" s="3"/>
     </row>
-    <row r="345" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -13778,7 +14046,7 @@
       <c r="AT345" s="3"/>
       <c r="AU345" s="3"/>
     </row>
-    <row r="346" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -13805,7 +14073,7 @@
       <c r="AT346" s="3"/>
       <c r="AU346" s="3"/>
     </row>
-    <row r="347" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -13832,7 +14100,7 @@
       <c r="AT347" s="3"/>
       <c r="AU347" s="3"/>
     </row>
-    <row r="348" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -13859,7 +14127,7 @@
       <c r="AT348" s="3"/>
       <c r="AU348" s="3"/>
     </row>
-    <row r="349" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -13886,7 +14154,7 @@
       <c r="AT349" s="3"/>
       <c r="AU349" s="3"/>
     </row>
-    <row r="350" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -13913,7 +14181,7 @@
       <c r="AT350" s="3"/>
       <c r="AU350" s="3"/>
     </row>
-    <row r="351" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -13940,7 +14208,7 @@
       <c r="AT351" s="3"/>
       <c r="AU351" s="3"/>
     </row>
-    <row r="352" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -13967,7 +14235,7 @@
       <c r="AT352" s="3"/>
       <c r="AU352" s="3"/>
     </row>
-    <row r="353" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -13994,7 +14262,7 @@
       <c r="AT353" s="3"/>
       <c r="AU353" s="3"/>
     </row>
-    <row r="354" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -14021,7 +14289,7 @@
       <c r="AT354" s="3"/>
       <c r="AU354" s="3"/>
     </row>
-    <row r="355" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -14048,7 +14316,7 @@
       <c r="AT355" s="3"/>
       <c r="AU355" s="3"/>
     </row>
-    <row r="356" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -14075,7 +14343,7 @@
       <c r="AT356" s="3"/>
       <c r="AU356" s="3"/>
     </row>
-    <row r="357" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -14102,7 +14370,7 @@
       <c r="AT357" s="3"/>
       <c r="AU357" s="3"/>
     </row>
-    <row r="358" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -14129,7 +14397,7 @@
       <c r="AT358" s="3"/>
       <c r="AU358" s="3"/>
     </row>
-    <row r="359" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -14156,7 +14424,7 @@
       <c r="AT359" s="3"/>
       <c r="AU359" s="3"/>
     </row>
-    <row r="360" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -14183,7 +14451,7 @@
       <c r="AT360" s="3"/>
       <c r="AU360" s="3"/>
     </row>
-    <row r="361" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -14210,7 +14478,7 @@
       <c r="AT361" s="3"/>
       <c r="AU361" s="3"/>
     </row>
-    <row r="362" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -14237,7 +14505,7 @@
       <c r="AT362" s="3"/>
       <c r="AU362" s="3"/>
     </row>
-    <row r="363" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -14264,7 +14532,7 @@
       <c r="AT363" s="3"/>
       <c r="AU363" s="3"/>
     </row>
-    <row r="364" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -14291,7 +14559,7 @@
       <c r="AT364" s="3"/>
       <c r="AU364" s="3"/>
     </row>
-    <row r="365" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -14318,7 +14586,7 @@
       <c r="AT365" s="3"/>
       <c r="AU365" s="3"/>
     </row>
-    <row r="366" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -14345,7 +14613,7 @@
       <c r="AT366" s="3"/>
       <c r="AU366" s="3"/>
     </row>
-    <row r="367" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -14372,7 +14640,7 @@
       <c r="AT367" s="3"/>
       <c r="AU367" s="3"/>
     </row>
-    <row r="368" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -14399,7 +14667,7 @@
       <c r="AT368" s="3"/>
       <c r="AU368" s="3"/>
     </row>
-    <row r="369" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -14426,7 +14694,7 @@
       <c r="AT369" s="3"/>
       <c r="AU369" s="3"/>
     </row>
-    <row r="370" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -14453,7 +14721,7 @@
       <c r="AT370" s="3"/>
       <c r="AU370" s="3"/>
     </row>
-    <row r="371" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -14480,7 +14748,7 @@
       <c r="AT371" s="3"/>
       <c r="AU371" s="3"/>
     </row>
-    <row r="372" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -14507,7 +14775,7 @@
       <c r="AT372" s="3"/>
       <c r="AU372" s="3"/>
     </row>
-    <row r="373" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -14534,7 +14802,7 @@
       <c r="AT373" s="3"/>
       <c r="AU373" s="3"/>
     </row>
-    <row r="374" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -14561,7 +14829,7 @@
       <c r="AT374" s="3"/>
       <c r="AU374" s="3"/>
     </row>
-    <row r="375" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -14588,7 +14856,7 @@
       <c r="AT375" s="3"/>
       <c r="AU375" s="3"/>
     </row>
-    <row r="376" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -14615,7 +14883,7 @@
       <c r="AT376" s="3"/>
       <c r="AU376" s="3"/>
     </row>
-    <row r="377" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -14642,7 +14910,7 @@
       <c r="AT377" s="3"/>
       <c r="AU377" s="3"/>
     </row>
-    <row r="378" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -14669,7 +14937,7 @@
       <c r="AT378" s="3"/>
       <c r="AU378" s="3"/>
     </row>
-    <row r="379" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -14696,7 +14964,7 @@
       <c r="AT379" s="3"/>
       <c r="AU379" s="3"/>
     </row>
-    <row r="380" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -14723,7 +14991,7 @@
       <c r="AT380" s="3"/>
       <c r="AU380" s="3"/>
     </row>
-    <row r="381" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -14750,7 +15018,7 @@
       <c r="AT381" s="3"/>
       <c r="AU381" s="3"/>
     </row>
-    <row r="382" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -14777,7 +15045,7 @@
       <c r="AT382" s="3"/>
       <c r="AU382" s="3"/>
     </row>
-    <row r="383" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -14804,7 +15072,7 @@
       <c r="AT383" s="3"/>
       <c r="AU383" s="3"/>
     </row>
-    <row r="384" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -14831,7 +15099,7 @@
       <c r="AT384" s="3"/>
       <c r="AU384" s="3"/>
     </row>
-    <row r="385" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -14858,7 +15126,7 @@
       <c r="AT385" s="3"/>
       <c r="AU385" s="3"/>
     </row>
-    <row r="386" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -14885,7 +15153,7 @@
       <c r="AT386" s="3"/>
       <c r="AU386" s="3"/>
     </row>
-    <row r="387" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -14912,7 +15180,7 @@
       <c r="AT387" s="3"/>
       <c r="AU387" s="3"/>
     </row>
-    <row r="388" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -14939,7 +15207,7 @@
       <c r="AT388" s="3"/>
       <c r="AU388" s="3"/>
     </row>
-    <row r="389" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -14966,7 +15234,7 @@
       <c r="AT389" s="3"/>
       <c r="AU389" s="3"/>
     </row>
-    <row r="390" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -14993,7 +15261,7 @@
       <c r="AT390" s="3"/>
       <c r="AU390" s="3"/>
     </row>
-    <row r="391" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -15020,7 +15288,7 @@
       <c r="AT391" s="3"/>
       <c r="AU391" s="3"/>
     </row>
-    <row r="392" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -15047,7 +15315,7 @@
       <c r="AT392" s="3"/>
       <c r="AU392" s="3"/>
     </row>
-    <row r="393" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -15074,7 +15342,7 @@
       <c r="AT393" s="3"/>
       <c r="AU393" s="3"/>
     </row>
-    <row r="394" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -15101,7 +15369,7 @@
       <c r="AT394" s="3"/>
       <c r="AU394" s="3"/>
     </row>
-    <row r="395" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -15128,7 +15396,7 @@
       <c r="AT395" s="3"/>
       <c r="AU395" s="3"/>
     </row>
-    <row r="396" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -15155,7 +15423,7 @@
       <c r="AT396" s="3"/>
       <c r="AU396" s="3"/>
     </row>
-    <row r="397" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -15182,7 +15450,7 @@
       <c r="AT397" s="3"/>
       <c r="AU397" s="3"/>
     </row>
-    <row r="398" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -15209,7 +15477,7 @@
       <c r="AT398" s="3"/>
       <c r="AU398" s="3"/>
     </row>
-    <row r="399" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -15236,7 +15504,7 @@
       <c r="AT399" s="3"/>
       <c r="AU399" s="3"/>
     </row>
-    <row r="400" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -15263,7 +15531,7 @@
       <c r="AT400" s="3"/>
       <c r="AU400" s="3"/>
     </row>
-    <row r="401" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -15290,7 +15558,7 @@
       <c r="AT401" s="3"/>
       <c r="AU401" s="3"/>
     </row>
-    <row r="402" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -15317,7 +15585,7 @@
       <c r="AT402" s="3"/>
       <c r="AU402" s="3"/>
     </row>
-    <row r="403" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -15344,7 +15612,7 @@
       <c r="AT403" s="3"/>
       <c r="AU403" s="3"/>
     </row>
-    <row r="404" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -15371,7 +15639,7 @@
       <c r="AT404" s="3"/>
       <c r="AU404" s="3"/>
     </row>
-    <row r="405" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -15398,7 +15666,7 @@
       <c r="AT405" s="3"/>
       <c r="AU405" s="3"/>
     </row>
-    <row r="406" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -15425,7 +15693,7 @@
       <c r="AT406" s="3"/>
       <c r="AU406" s="3"/>
     </row>
-    <row r="407" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -15452,7 +15720,7 @@
       <c r="AT407" s="3"/>
       <c r="AU407" s="3"/>
     </row>
-    <row r="408" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -15479,7 +15747,7 @@
       <c r="AT408" s="3"/>
       <c r="AU408" s="3"/>
     </row>
-    <row r="409" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -15506,7 +15774,7 @@
       <c r="AT409" s="3"/>
       <c r="AU409" s="3"/>
     </row>
-    <row r="410" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -15533,7 +15801,7 @@
       <c r="AT410" s="3"/>
       <c r="AU410" s="3"/>
     </row>
-    <row r="411" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -15560,7 +15828,7 @@
       <c r="AT411" s="3"/>
       <c r="AU411" s="3"/>
     </row>
-    <row r="412" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -15587,7 +15855,7 @@
       <c r="AT412" s="3"/>
       <c r="AU412" s="3"/>
     </row>
-    <row r="413" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -15614,7 +15882,7 @@
       <c r="AT413" s="3"/>
       <c r="AU413" s="3"/>
     </row>
-    <row r="414" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -15641,7 +15909,7 @@
       <c r="AT414" s="3"/>
       <c r="AU414" s="3"/>
     </row>
-    <row r="415" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -15668,7 +15936,7 @@
       <c r="AT415" s="3"/>
       <c r="AU415" s="3"/>
     </row>
-    <row r="416" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -15695,7 +15963,7 @@
       <c r="AT416" s="3"/>
       <c r="AU416" s="3"/>
     </row>
-    <row r="417" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -15722,7 +15990,7 @@
       <c r="AT417" s="3"/>
       <c r="AU417" s="3"/>
     </row>
-    <row r="418" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -15749,7 +16017,7 @@
       <c r="AT418" s="3"/>
       <c r="AU418" s="3"/>
     </row>
-    <row r="419" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -15776,7 +16044,7 @@
       <c r="AT419" s="3"/>
       <c r="AU419" s="3"/>
     </row>
-    <row r="420" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -15803,7 +16071,7 @@
       <c r="AT420" s="3"/>
       <c r="AU420" s="3"/>
     </row>
-    <row r="421" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -15830,7 +16098,7 @@
       <c r="AT421" s="3"/>
       <c r="AU421" s="3"/>
     </row>
-    <row r="422" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -15857,7 +16125,7 @@
       <c r="AT422" s="3"/>
       <c r="AU422" s="3"/>
     </row>
-    <row r="423" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -15884,7 +16152,7 @@
       <c r="AT423" s="3"/>
       <c r="AU423" s="3"/>
     </row>
-    <row r="424" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -15911,7 +16179,7 @@
       <c r="AT424" s="3"/>
       <c r="AU424" s="3"/>
     </row>
-    <row r="425" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -15938,7 +16206,7 @@
       <c r="AT425" s="3"/>
       <c r="AU425" s="3"/>
     </row>
-    <row r="426" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -15965,7 +16233,7 @@
       <c r="AT426" s="3"/>
       <c r="AU426" s="3"/>
     </row>
-    <row r="427" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -15992,7 +16260,7 @@
       <c r="AT427" s="3"/>
       <c r="AU427" s="3"/>
     </row>
-    <row r="428" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -16019,7 +16287,7 @@
       <c r="AT428" s="3"/>
       <c r="AU428" s="3"/>
     </row>
-    <row r="429" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -16046,7 +16314,7 @@
       <c r="AT429" s="3"/>
       <c r="AU429" s="3"/>
     </row>
-    <row r="430" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -16073,7 +16341,7 @@
       <c r="AT430" s="3"/>
       <c r="AU430" s="3"/>
     </row>
-    <row r="431" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -16100,7 +16368,7 @@
       <c r="AT431" s="3"/>
       <c r="AU431" s="3"/>
     </row>
-    <row r="432" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -16127,7 +16395,7 @@
       <c r="AT432" s="3"/>
       <c r="AU432" s="3"/>
     </row>
-    <row r="433" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -16154,7 +16422,7 @@
       <c r="AT433" s="3"/>
       <c r="AU433" s="3"/>
     </row>
-    <row r="434" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -16181,7 +16449,7 @@
       <c r="AT434" s="3"/>
       <c r="AU434" s="3"/>
     </row>
-    <row r="435" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -16208,7 +16476,7 @@
       <c r="AT435" s="3"/>
       <c r="AU435" s="3"/>
     </row>
-    <row r="436" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -16235,7 +16503,7 @@
       <c r="AT436" s="3"/>
       <c r="AU436" s="3"/>
     </row>
-    <row r="437" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -16262,7 +16530,7 @@
       <c r="AT437" s="3"/>
       <c r="AU437" s="3"/>
     </row>
-    <row r="438" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -16289,7 +16557,7 @@
       <c r="AT438" s="3"/>
       <c r="AU438" s="3"/>
     </row>
-    <row r="439" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -16316,7 +16584,7 @@
       <c r="AT439" s="3"/>
       <c r="AU439" s="3"/>
     </row>
-    <row r="440" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -16343,7 +16611,7 @@
       <c r="AT440" s="3"/>
       <c r="AU440" s="3"/>
     </row>
-    <row r="441" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -16370,7 +16638,7 @@
       <c r="AT441" s="3"/>
       <c r="AU441" s="3"/>
     </row>
-    <row r="442" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -16397,7 +16665,7 @@
       <c r="AT442" s="3"/>
       <c r="AU442" s="3"/>
     </row>
-    <row r="443" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -16424,7 +16692,7 @@
       <c r="AT443" s="3"/>
       <c r="AU443" s="3"/>
     </row>
-    <row r="444" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -16451,7 +16719,7 @@
       <c r="AT444" s="3"/>
       <c r="AU444" s="3"/>
     </row>
-    <row r="445" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -16478,7 +16746,7 @@
       <c r="AT445" s="3"/>
       <c r="AU445" s="3"/>
     </row>
-    <row r="446" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -16505,7 +16773,7 @@
       <c r="AT446" s="3"/>
       <c r="AU446" s="3"/>
     </row>
-    <row r="447" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -16532,7 +16800,7 @@
       <c r="AT447" s="3"/>
       <c r="AU447" s="3"/>
     </row>
-    <row r="448" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -16559,7 +16827,7 @@
       <c r="AT448" s="3"/>
       <c r="AU448" s="3"/>
     </row>
-    <row r="449" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -16586,7 +16854,7 @@
       <c r="AT449" s="3"/>
       <c r="AU449" s="3"/>
     </row>
-    <row r="450" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -16613,7 +16881,7 @@
       <c r="AT450" s="3"/>
       <c r="AU450" s="3"/>
     </row>
-    <row r="451" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -16640,7 +16908,7 @@
       <c r="AT451" s="3"/>
       <c r="AU451" s="3"/>
     </row>
-    <row r="452" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -16667,7 +16935,7 @@
       <c r="AT452" s="3"/>
       <c r="AU452" s="3"/>
     </row>
-    <row r="453" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -16694,7 +16962,7 @@
       <c r="AT453" s="3"/>
       <c r="AU453" s="3"/>
     </row>
-    <row r="454" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -16721,7 +16989,7 @@
       <c r="AT454" s="3"/>
       <c r="AU454" s="3"/>
     </row>
-    <row r="455" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -16748,7 +17016,7 @@
       <c r="AT455" s="3"/>
       <c r="AU455" s="3"/>
     </row>
-    <row r="456" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -16775,7 +17043,7 @@
       <c r="AT456" s="3"/>
       <c r="AU456" s="3"/>
     </row>
-    <row r="457" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -16802,7 +17070,7 @@
       <c r="AT457" s="3"/>
       <c r="AU457" s="3"/>
     </row>
-    <row r="458" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -16829,7 +17097,7 @@
       <c r="AT458" s="3"/>
       <c r="AU458" s="3"/>
     </row>
-    <row r="459" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -16856,7 +17124,7 @@
       <c r="AT459" s="3"/>
       <c r="AU459" s="3"/>
     </row>
-    <row r="460" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -16883,7 +17151,7 @@
       <c r="AT460" s="3"/>
       <c r="AU460" s="3"/>
     </row>
-    <row r="461" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -16910,7 +17178,7 @@
       <c r="AT461" s="3"/>
       <c r="AU461" s="3"/>
     </row>
-    <row r="462" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -16937,7 +17205,7 @@
       <c r="AT462" s="3"/>
       <c r="AU462" s="3"/>
     </row>
-    <row r="463" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -16964,7 +17232,7 @@
       <c r="AT463" s="3"/>
       <c r="AU463" s="3"/>
     </row>
-    <row r="464" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -16991,7 +17259,7 @@
       <c r="AT464" s="3"/>
       <c r="AU464" s="3"/>
     </row>
-    <row r="465" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -17018,7 +17286,7 @@
       <c r="AT465" s="3"/>
       <c r="AU465" s="3"/>
     </row>
-    <row r="466" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -17045,7 +17313,7 @@
       <c r="AT466" s="3"/>
       <c r="AU466" s="3"/>
     </row>
-    <row r="467" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -17072,7 +17340,7 @@
       <c r="AT467" s="3"/>
       <c r="AU467" s="3"/>
     </row>
-    <row r="468" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -17099,7 +17367,7 @@
       <c r="AT468" s="3"/>
       <c r="AU468" s="3"/>
     </row>
-    <row r="469" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -17126,7 +17394,7 @@
       <c r="AT469" s="3"/>
       <c r="AU469" s="3"/>
     </row>
-    <row r="470" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -17153,7 +17421,7 @@
       <c r="AT470" s="3"/>
       <c r="AU470" s="3"/>
     </row>
-    <row r="471" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -17180,7 +17448,7 @@
       <c r="AT471" s="3"/>
       <c r="AU471" s="3"/>
     </row>
-    <row r="472" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -17207,7 +17475,7 @@
       <c r="AT472" s="3"/>
       <c r="AU472" s="3"/>
     </row>
-    <row r="473" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -17234,7 +17502,7 @@
       <c r="AT473" s="3"/>
       <c r="AU473" s="3"/>
     </row>
-    <row r="474" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -17261,7 +17529,7 @@
       <c r="AT474" s="3"/>
       <c r="AU474" s="3"/>
     </row>
-    <row r="475" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -17288,7 +17556,7 @@
       <c r="AT475" s="3"/>
       <c r="AU475" s="3"/>
     </row>
-    <row r="476" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -17315,7 +17583,7 @@
       <c r="AT476" s="3"/>
       <c r="AU476" s="3"/>
     </row>
-    <row r="477" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -17342,7 +17610,7 @@
       <c r="AT477" s="3"/>
       <c r="AU477" s="3"/>
     </row>
-    <row r="478" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -17369,7 +17637,7 @@
       <c r="AT478" s="3"/>
       <c r="AU478" s="3"/>
     </row>
-    <row r="479" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -17396,7 +17664,7 @@
       <c r="AT479" s="3"/>
       <c r="AU479" s="3"/>
     </row>
-    <row r="480" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -17423,7 +17691,7 @@
       <c r="AT480" s="3"/>
       <c r="AU480" s="3"/>
     </row>
-    <row r="481" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -17450,7 +17718,7 @@
       <c r="AT481" s="3"/>
       <c r="AU481" s="3"/>
     </row>
-    <row r="482" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -17477,7 +17745,7 @@
       <c r="AT482" s="3"/>
       <c r="AU482" s="3"/>
     </row>
-    <row r="483" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -17504,7 +17772,7 @@
       <c r="AT483" s="3"/>
       <c r="AU483" s="3"/>
     </row>
-    <row r="484" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -17531,7 +17799,7 @@
       <c r="AT484" s="3"/>
       <c r="AU484" s="3"/>
     </row>
-    <row r="485" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -17558,7 +17826,7 @@
       <c r="AT485" s="3"/>
       <c r="AU485" s="3"/>
     </row>
-    <row r="486" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -17585,7 +17853,7 @@
       <c r="AT486" s="3"/>
       <c r="AU486" s="3"/>
     </row>
-    <row r="487" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -17612,7 +17880,7 @@
       <c r="AT487" s="3"/>
       <c r="AU487" s="3"/>
     </row>
-    <row r="488" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -17639,7 +17907,7 @@
       <c r="AT488" s="3"/>
       <c r="AU488" s="3"/>
     </row>
-    <row r="489" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -17666,7 +17934,7 @@
       <c r="AT489" s="3"/>
       <c r="AU489" s="3"/>
     </row>
-    <row r="490" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -17693,7 +17961,7 @@
       <c r="AT490" s="3"/>
       <c r="AU490" s="3"/>
     </row>
-    <row r="491" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -17720,7 +17988,7 @@
       <c r="AT491" s="3"/>
       <c r="AU491" s="3"/>
     </row>
-    <row r="492" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -17747,7 +18015,7 @@
       <c r="AT492" s="3"/>
       <c r="AU492" s="3"/>
     </row>
-    <row r="493" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -17774,7 +18042,7 @@
       <c r="AT493" s="3"/>
       <c r="AU493" s="3"/>
     </row>
-    <row r="494" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -17801,7 +18069,7 @@
       <c r="AT494" s="3"/>
       <c r="AU494" s="3"/>
     </row>
-    <row r="495" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -17828,7 +18096,7 @@
       <c r="AT495" s="3"/>
       <c r="AU495" s="3"/>
     </row>
-    <row r="496" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -17855,7 +18123,7 @@
       <c r="AT496" s="3"/>
       <c r="AU496" s="3"/>
     </row>
-    <row r="497" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -17882,7 +18150,7 @@
       <c r="AT497" s="3"/>
       <c r="AU497" s="3"/>
     </row>
-    <row r="498" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -17909,7 +18177,7 @@
       <c r="AT498" s="3"/>
       <c r="AU498" s="3"/>
     </row>
-    <row r="499" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -17936,7 +18204,7 @@
       <c r="AT499" s="3"/>
       <c r="AU499" s="3"/>
     </row>
-    <row r="500" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -17963,7 +18231,7 @@
       <c r="AT500" s="3"/>
       <c r="AU500" s="3"/>
     </row>
-    <row r="501" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -17990,7 +18258,7 @@
       <c r="AT501" s="3"/>
       <c r="AU501" s="3"/>
     </row>
-    <row r="502" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -18017,7 +18285,7 @@
       <c r="AT502" s="3"/>
       <c r="AU502" s="3"/>
     </row>
-    <row r="503" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -18044,7 +18312,7 @@
       <c r="AT503" s="3"/>
       <c r="AU503" s="3"/>
     </row>
-    <row r="504" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -18071,7 +18339,7 @@
       <c r="AT504" s="3"/>
       <c r="AU504" s="3"/>
     </row>
-    <row r="505" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -18098,7 +18366,7 @@
       <c r="AT505" s="3"/>
       <c r="AU505" s="3"/>
     </row>
-    <row r="506" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
@@ -18125,7 +18393,7 @@
       <c r="AT506" s="3"/>
       <c r="AU506" s="3"/>
     </row>
-    <row r="507" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -18152,7 +18420,7 @@
       <c r="AT507" s="3"/>
       <c r="AU507" s="3"/>
     </row>
-    <row r="508" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -18179,7 +18447,7 @@
       <c r="AT508" s="3"/>
       <c r="AU508" s="3"/>
     </row>
-    <row r="509" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -18206,7 +18474,7 @@
       <c r="AT509" s="3"/>
       <c r="AU509" s="3"/>
     </row>
-    <row r="510" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -18233,7 +18501,7 @@
       <c r="AT510" s="3"/>
       <c r="AU510" s="3"/>
     </row>
-    <row r="511" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -18260,7 +18528,7 @@
       <c r="AT511" s="3"/>
       <c r="AU511" s="3"/>
     </row>
-    <row r="512" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
@@ -18287,7 +18555,7 @@
       <c r="AT512" s="3"/>
       <c r="AU512" s="3"/>
     </row>
-    <row r="513" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -18314,7 +18582,7 @@
       <c r="AT513" s="3"/>
       <c r="AU513" s="3"/>
     </row>
-    <row r="514" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -18341,7 +18609,7 @@
       <c r="AT514" s="3"/>
       <c r="AU514" s="3"/>
     </row>
-    <row r="515" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -18368,7 +18636,7 @@
       <c r="AT515" s="3"/>
       <c r="AU515" s="3"/>
     </row>
-    <row r="516" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -18395,7 +18663,7 @@
       <c r="AT516" s="3"/>
       <c r="AU516" s="3"/>
     </row>
-    <row r="517" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -18422,7 +18690,7 @@
       <c r="AT517" s="3"/>
       <c r="AU517" s="3"/>
     </row>
-    <row r="518" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -18449,7 +18717,7 @@
       <c r="AT518" s="3"/>
       <c r="AU518" s="3"/>
     </row>
-    <row r="519" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -18476,7 +18744,7 @@
       <c r="AT519" s="3"/>
       <c r="AU519" s="3"/>
     </row>
-    <row r="520" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -18503,7 +18771,7 @@
       <c r="AT520" s="3"/>
       <c r="AU520" s="3"/>
     </row>
-    <row r="521" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -18530,7 +18798,7 @@
       <c r="AT521" s="3"/>
       <c r="AU521" s="3"/>
     </row>
-    <row r="522" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
@@ -18557,7 +18825,7 @@
       <c r="AT522" s="3"/>
       <c r="AU522" s="3"/>
     </row>
-    <row r="523" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -18584,7 +18852,7 @@
       <c r="AT523" s="3"/>
       <c r="AU523" s="3"/>
     </row>
-    <row r="524" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -18611,7 +18879,7 @@
       <c r="AT524" s="3"/>
       <c r="AU524" s="3"/>
     </row>
-    <row r="525" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -18638,7 +18906,7 @@
       <c r="AT525" s="3"/>
       <c r="AU525" s="3"/>
     </row>
-    <row r="526" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -18665,7 +18933,7 @@
       <c r="AT526" s="3"/>
       <c r="AU526" s="3"/>
     </row>
-    <row r="527" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -18692,7 +18960,7 @@
       <c r="AT527" s="3"/>
       <c r="AU527" s="3"/>
     </row>
-    <row r="528" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -18719,7 +18987,7 @@
       <c r="AT528" s="3"/>
       <c r="AU528" s="3"/>
     </row>
-    <row r="529" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -18746,7 +19014,7 @@
       <c r="AT529" s="3"/>
       <c r="AU529" s="3"/>
     </row>
-    <row r="530" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -18773,7 +19041,7 @@
       <c r="AT530" s="3"/>
       <c r="AU530" s="3"/>
     </row>
-    <row r="531" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -18800,7 +19068,7 @@
       <c r="AT531" s="3"/>
       <c r="AU531" s="3"/>
     </row>
-    <row r="532" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -18827,7 +19095,7 @@
       <c r="AT532" s="3"/>
       <c r="AU532" s="3"/>
     </row>
-    <row r="533" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -18854,7 +19122,7 @@
       <c r="AT533" s="3"/>
       <c r="AU533" s="3"/>
     </row>
-    <row r="534" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
@@ -18881,7 +19149,7 @@
       <c r="AT534" s="3"/>
       <c r="AU534" s="3"/>
     </row>
-    <row r="535" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -18908,7 +19176,7 @@
       <c r="AT535" s="3"/>
       <c r="AU535" s="3"/>
     </row>
-    <row r="536" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -18935,7 +19203,7 @@
       <c r="AT536" s="3"/>
       <c r="AU536" s="3"/>
     </row>
-    <row r="537" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -18962,7 +19230,7 @@
       <c r="AT537" s="3"/>
       <c r="AU537" s="3"/>
     </row>
-    <row r="538" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -18989,7 +19257,7 @@
       <c r="AT538" s="3"/>
       <c r="AU538" s="3"/>
     </row>
-    <row r="539" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -19016,7 +19284,7 @@
       <c r="AT539" s="3"/>
       <c r="AU539" s="3"/>
     </row>
-    <row r="540" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
@@ -19043,7 +19311,7 @@
       <c r="AT540" s="3"/>
       <c r="AU540" s="3"/>
     </row>
-    <row r="541" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -19070,7 +19338,7 @@
       <c r="AT541" s="3"/>
       <c r="AU541" s="3"/>
     </row>
-    <row r="542" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
@@ -19097,7 +19365,7 @@
       <c r="AT542" s="3"/>
       <c r="AU542" s="3"/>
     </row>
-    <row r="543" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -19124,7 +19392,7 @@
       <c r="AT543" s="3"/>
       <c r="AU543" s="3"/>
     </row>
-    <row r="544" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -19151,7 +19419,7 @@
       <c r="AT544" s="3"/>
       <c r="AU544" s="3"/>
     </row>
-    <row r="545" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -19178,7 +19446,7 @@
       <c r="AT545" s="3"/>
       <c r="AU545" s="3"/>
     </row>
-    <row r="546" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -19205,7 +19473,7 @@
       <c r="AT546" s="3"/>
       <c r="AU546" s="3"/>
     </row>
-    <row r="547" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -19232,7 +19500,7 @@
       <c r="AT547" s="3"/>
       <c r="AU547" s="3"/>
     </row>
-    <row r="548" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -19259,7 +19527,7 @@
       <c r="AT548" s="3"/>
       <c r="AU548" s="3"/>
     </row>
-    <row r="549" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -19286,7 +19554,7 @@
       <c r="AT549" s="3"/>
       <c r="AU549" s="3"/>
     </row>
-    <row r="550" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -19313,7 +19581,7 @@
       <c r="AT550" s="3"/>
       <c r="AU550" s="3"/>
     </row>
-    <row r="551" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
@@ -19340,7 +19608,7 @@
       <c r="AT551" s="3"/>
       <c r="AU551" s="3"/>
     </row>
-    <row r="552" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -19367,7 +19635,7 @@
       <c r="AT552" s="3"/>
       <c r="AU552" s="3"/>
     </row>
-    <row r="553" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -19394,7 +19662,7 @@
       <c r="AT553" s="3"/>
       <c r="AU553" s="3"/>
     </row>
-    <row r="554" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -19421,7 +19689,7 @@
       <c r="AT554" s="3"/>
       <c r="AU554" s="3"/>
     </row>
-    <row r="555" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -19448,7 +19716,7 @@
       <c r="AT555" s="3"/>
       <c r="AU555" s="3"/>
     </row>
-    <row r="556" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
@@ -19475,7 +19743,7 @@
       <c r="AT556" s="3"/>
       <c r="AU556" s="3"/>
     </row>
-    <row r="557" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -19502,7 +19770,7 @@
       <c r="AT557" s="3"/>
       <c r="AU557" s="3"/>
     </row>
-    <row r="558" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -19529,7 +19797,7 @@
       <c r="AT558" s="3"/>
       <c r="AU558" s="3"/>
     </row>
-    <row r="559" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
@@ -19556,7 +19824,7 @@
       <c r="AT559" s="3"/>
       <c r="AU559" s="3"/>
     </row>
-    <row r="560" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -19583,7 +19851,7 @@
       <c r="AT560" s="3"/>
       <c r="AU560" s="3"/>
     </row>
-    <row r="561" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -19610,7 +19878,7 @@
       <c r="AT561" s="3"/>
       <c r="AU561" s="3"/>
     </row>
-    <row r="562" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -19637,7 +19905,7 @@
       <c r="AT562" s="3"/>
       <c r="AU562" s="3"/>
     </row>
-    <row r="563" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -19664,7 +19932,7 @@
       <c r="AT563" s="3"/>
       <c r="AU563" s="3"/>
     </row>
-    <row r="564" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -19691,7 +19959,7 @@
       <c r="AT564" s="3"/>
       <c r="AU564" s="3"/>
     </row>
-    <row r="565" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
@@ -19718,7 +19986,7 @@
       <c r="AT565" s="3"/>
       <c r="AU565" s="3"/>
     </row>
-    <row r="566" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -19745,7 +20013,7 @@
       <c r="AT566" s="3"/>
       <c r="AU566" s="3"/>
     </row>
-    <row r="567" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -19772,7 +20040,7 @@
       <c r="AT567" s="3"/>
       <c r="AU567" s="3"/>
     </row>
-    <row r="568" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
@@ -19799,7 +20067,7 @@
       <c r="AT568" s="3"/>
       <c r="AU568" s="3"/>
     </row>
-    <row r="569" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -19826,7 +20094,7 @@
       <c r="AT569" s="3"/>
       <c r="AU569" s="3"/>
     </row>
-    <row r="570" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -19853,7 +20121,7 @@
       <c r="AT570" s="3"/>
       <c r="AU570" s="3"/>
     </row>
-    <row r="571" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -19880,7 +20148,7 @@
       <c r="AT571" s="3"/>
       <c r="AU571" s="3"/>
     </row>
-    <row r="572" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
@@ -19907,7 +20175,7 @@
       <c r="AT572" s="3"/>
       <c r="AU572" s="3"/>
     </row>
-    <row r="573" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -19934,7 +20202,7 @@
       <c r="AT573" s="3"/>
       <c r="AU573" s="3"/>
     </row>
-    <row r="574" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -19961,7 +20229,7 @@
       <c r="AT574" s="3"/>
       <c r="AU574" s="3"/>
     </row>
-    <row r="575" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -19988,7 +20256,7 @@
       <c r="AT575" s="3"/>
       <c r="AU575" s="3"/>
     </row>
-    <row r="576" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -20015,7 +20283,7 @@
       <c r="AT576" s="3"/>
       <c r="AU576" s="3"/>
     </row>
-    <row r="577" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -20042,7 +20310,7 @@
       <c r="AT577" s="3"/>
       <c r="AU577" s="3"/>
     </row>
-    <row r="578" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
@@ -20069,7 +20337,7 @@
       <c r="AT578" s="3"/>
       <c r="AU578" s="3"/>
     </row>
-    <row r="579" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
@@ -20096,7 +20364,7 @@
       <c r="AT579" s="3"/>
       <c r="AU579" s="3"/>
     </row>
-    <row r="580" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -20123,7 +20391,7 @@
       <c r="AT580" s="3"/>
       <c r="AU580" s="3"/>
     </row>
-    <row r="581" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -20150,7 +20418,7 @@
       <c r="AT581" s="3"/>
       <c r="AU581" s="3"/>
     </row>
-    <row r="582" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
@@ -20177,7 +20445,7 @@
       <c r="AT582" s="3"/>
       <c r="AU582" s="3"/>
     </row>
-    <row r="583" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -20204,7 +20472,7 @@
       <c r="AT583" s="3"/>
       <c r="AU583" s="3"/>
     </row>
-    <row r="584" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
@@ -20231,7 +20499,7 @@
       <c r="AT584" s="3"/>
       <c r="AU584" s="3"/>
     </row>
-    <row r="585" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -20258,7 +20526,7 @@
       <c r="AT585" s="3"/>
       <c r="AU585" s="3"/>
     </row>
-    <row r="586" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -20285,7 +20553,7 @@
       <c r="AT586" s="3"/>
       <c r="AU586" s="3"/>
     </row>
-    <row r="587" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -20312,7 +20580,7 @@
       <c r="AT587" s="3"/>
       <c r="AU587" s="3"/>
     </row>
-    <row r="588" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
@@ -20339,7 +20607,7 @@
       <c r="AT588" s="3"/>
       <c r="AU588" s="3"/>
     </row>
-    <row r="589" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -20366,7 +20634,7 @@
       <c r="AT589" s="3"/>
       <c r="AU589" s="3"/>
     </row>
-    <row r="590" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -20393,7 +20661,7 @@
       <c r="AT590" s="3"/>
       <c r="AU590" s="3"/>
     </row>
-    <row r="591" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -20420,7 +20688,7 @@
       <c r="AT591" s="3"/>
       <c r="AU591" s="3"/>
     </row>
-    <row r="592" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -20447,7 +20715,7 @@
       <c r="AT592" s="3"/>
       <c r="AU592" s="3"/>
     </row>
-    <row r="593" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
@@ -20474,7 +20742,7 @@
       <c r="AT593" s="3"/>
       <c r="AU593" s="3"/>
     </row>
-    <row r="594" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -20501,7 +20769,7 @@
       <c r="AT594" s="3"/>
       <c r="AU594" s="3"/>
     </row>
-    <row r="595" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -20528,7 +20796,7 @@
       <c r="AT595" s="3"/>
       <c r="AU595" s="3"/>
     </row>
-    <row r="596" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -20555,7 +20823,7 @@
       <c r="AT596" s="3"/>
       <c r="AU596" s="3"/>
     </row>
-    <row r="597" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -20582,7 +20850,7 @@
       <c r="AT597" s="3"/>
       <c r="AU597" s="3"/>
     </row>
-    <row r="598" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -20609,7 +20877,7 @@
       <c r="AT598" s="3"/>
       <c r="AU598" s="3"/>
     </row>
-    <row r="599" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
@@ -20636,7 +20904,7 @@
       <c r="AT599" s="3"/>
       <c r="AU599" s="3"/>
     </row>
-    <row r="600" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -20663,7 +20931,7 @@
       <c r="AT600" s="3"/>
       <c r="AU600" s="3"/>
     </row>
-    <row r="601" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -20690,7 +20958,7 @@
       <c r="AT601" s="3"/>
       <c r="AU601" s="3"/>
     </row>
-    <row r="602" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -20717,7 +20985,7 @@
       <c r="AT602" s="3"/>
       <c r="AU602" s="3"/>
     </row>
-    <row r="603" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -20744,7 +21012,7 @@
       <c r="AT603" s="3"/>
       <c r="AU603" s="3"/>
     </row>
-    <row r="604" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
@@ -20771,7 +21039,7 @@
       <c r="AT604" s="3"/>
       <c r="AU604" s="3"/>
     </row>
-    <row r="605" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
@@ -20798,7 +21066,7 @@
       <c r="AT605" s="3"/>
       <c r="AU605" s="3"/>
     </row>
-    <row r="606" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
@@ -20825,7 +21093,7 @@
       <c r="AT606" s="3"/>
       <c r="AU606" s="3"/>
     </row>
-    <row r="607" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
@@ -20852,7 +21120,7 @@
       <c r="AT607" s="3"/>
       <c r="AU607" s="3"/>
     </row>
-    <row r="608" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
@@ -20879,7 +21147,7 @@
       <c r="AT608" s="3"/>
       <c r="AU608" s="3"/>
     </row>
-    <row r="609" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
@@ -20906,7 +21174,7 @@
       <c r="AT609" s="3"/>
       <c r="AU609" s="3"/>
     </row>
-    <row r="610" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
@@ -20933,7 +21201,7 @@
       <c r="AT610" s="3"/>
       <c r="AU610" s="3"/>
     </row>
-    <row r="611" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
@@ -20960,7 +21228,7 @@
       <c r="AT611" s="3"/>
       <c r="AU611" s="3"/>
     </row>
-    <row r="612" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
@@ -20987,7 +21255,7 @@
       <c r="AT612" s="3"/>
       <c r="AU612" s="3"/>
     </row>
-    <row r="613" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
@@ -21014,7 +21282,7 @@
       <c r="AT613" s="3"/>
       <c r="AU613" s="3"/>
     </row>
-    <row r="614" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
@@ -21041,7 +21309,7 @@
       <c r="AT614" s="3"/>
       <c r="AU614" s="3"/>
     </row>
-    <row r="615" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
@@ -21068,7 +21336,7 @@
       <c r="AT615" s="3"/>
       <c r="AU615" s="3"/>
     </row>
-    <row r="616" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
@@ -21095,7 +21363,7 @@
       <c r="AT616" s="3"/>
       <c r="AU616" s="3"/>
     </row>
-    <row r="617" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
@@ -21122,7 +21390,7 @@
       <c r="AT617" s="3"/>
       <c r="AU617" s="3"/>
     </row>
-    <row r="618" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
@@ -21149,7 +21417,7 @@
       <c r="AT618" s="3"/>
       <c r="AU618" s="3"/>
     </row>
-    <row r="619" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
@@ -21176,7 +21444,7 @@
       <c r="AT619" s="3"/>
       <c r="AU619" s="3"/>
     </row>
-    <row r="620" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
@@ -21203,7 +21471,7 @@
       <c r="AT620" s="3"/>
       <c r="AU620" s="3"/>
     </row>
-    <row r="621" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
@@ -21230,7 +21498,7 @@
       <c r="AT621" s="3"/>
       <c r="AU621" s="3"/>
     </row>
-    <row r="622" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
@@ -21257,7 +21525,7 @@
       <c r="AT622" s="3"/>
       <c r="AU622" s="3"/>
     </row>
-    <row r="623" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
@@ -21284,7 +21552,7 @@
       <c r="AT623" s="3"/>
       <c r="AU623" s="3"/>
     </row>
-    <row r="624" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
@@ -21311,7 +21579,7 @@
       <c r="AT624" s="3"/>
       <c r="AU624" s="3"/>
     </row>
-    <row r="625" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
@@ -21338,7 +21606,7 @@
       <c r="AT625" s="3"/>
       <c r="AU625" s="3"/>
     </row>
-    <row r="626" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
@@ -21365,7 +21633,7 @@
       <c r="AT626" s="3"/>
       <c r="AU626" s="3"/>
     </row>
-    <row r="627" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
@@ -21392,7 +21660,7 @@
       <c r="AT627" s="3"/>
       <c r="AU627" s="3"/>
     </row>
-    <row r="628" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
@@ -21419,7 +21687,7 @@
       <c r="AT628" s="3"/>
       <c r="AU628" s="3"/>
     </row>
-    <row r="629" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
@@ -21446,7 +21714,7 @@
       <c r="AT629" s="3"/>
       <c r="AU629" s="3"/>
     </row>
-    <row r="630" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
@@ -21473,7 +21741,7 @@
       <c r="AT630" s="3"/>
       <c r="AU630" s="3"/>
     </row>
-    <row r="631" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
@@ -21500,7 +21768,7 @@
       <c r="AT631" s="3"/>
       <c r="AU631" s="3"/>
     </row>
-    <row r="632" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
@@ -21527,7 +21795,7 @@
       <c r="AT632" s="3"/>
       <c r="AU632" s="3"/>
     </row>
-    <row r="633" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
@@ -21554,7 +21822,7 @@
       <c r="AT633" s="3"/>
       <c r="AU633" s="3"/>
     </row>
-    <row r="634" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
@@ -21581,7 +21849,7 @@
       <c r="AT634" s="3"/>
       <c r="AU634" s="3"/>
     </row>
-    <row r="635" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
@@ -21608,7 +21876,7 @@
       <c r="AT635" s="3"/>
       <c r="AU635" s="3"/>
     </row>
-    <row r="636" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
@@ -21635,7 +21903,7 @@
       <c r="AT636" s="3"/>
       <c r="AU636" s="3"/>
     </row>
-    <row r="637" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
@@ -21662,7 +21930,7 @@
       <c r="AT637" s="3"/>
       <c r="AU637" s="3"/>
     </row>
-    <row r="638" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
@@ -21689,7 +21957,7 @@
       <c r="AT638" s="3"/>
       <c r="AU638" s="3"/>
     </row>
-    <row r="639" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
@@ -21716,7 +21984,7 @@
       <c r="AT639" s="3"/>
       <c r="AU639" s="3"/>
     </row>
-    <row r="640" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
@@ -21743,7 +22011,7 @@
       <c r="AT640" s="3"/>
       <c r="AU640" s="3"/>
     </row>
-    <row r="641" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
@@ -21770,7 +22038,7 @@
       <c r="AT641" s="3"/>
       <c r="AU641" s="3"/>
     </row>
-    <row r="642" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
@@ -21797,7 +22065,7 @@
       <c r="AT642" s="3"/>
       <c r="AU642" s="3"/>
     </row>
-    <row r="643" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
@@ -21824,7 +22092,7 @@
       <c r="AT643" s="3"/>
       <c r="AU643" s="3"/>
     </row>
-    <row r="644" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
@@ -21851,7 +22119,7 @@
       <c r="AT644" s="3"/>
       <c r="AU644" s="3"/>
     </row>
-    <row r="645" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
@@ -21878,7 +22146,7 @@
       <c r="AT645" s="3"/>
       <c r="AU645" s="3"/>
     </row>
-    <row r="646" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
@@ -21905,7 +22173,7 @@
       <c r="AT646" s="3"/>
       <c r="AU646" s="3"/>
     </row>
-    <row r="647" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
@@ -21932,7 +22200,7 @@
       <c r="AT647" s="3"/>
       <c r="AU647" s="3"/>
     </row>
-    <row r="648" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
@@ -21959,7 +22227,7 @@
       <c r="AT648" s="3"/>
       <c r="AU648" s="3"/>
     </row>
-    <row r="649" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
@@ -21986,7 +22254,7 @@
       <c r="AT649" s="3"/>
       <c r="AU649" s="3"/>
     </row>
-    <row r="650" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
@@ -22013,7 +22281,7 @@
       <c r="AT650" s="3"/>
       <c r="AU650" s="3"/>
     </row>
-    <row r="651" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
@@ -22040,7 +22308,7 @@
       <c r="AT651" s="3"/>
       <c r="AU651" s="3"/>
     </row>
-    <row r="652" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
@@ -22067,7 +22335,7 @@
       <c r="AT652" s="3"/>
       <c r="AU652" s="3"/>
     </row>
-    <row r="653" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
@@ -22094,7 +22362,7 @@
       <c r="AT653" s="3"/>
       <c r="AU653" s="3"/>
     </row>
-    <row r="654" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
@@ -22121,7 +22389,7 @@
       <c r="AT654" s="3"/>
       <c r="AU654" s="3"/>
     </row>
-    <row r="655" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
@@ -22148,7 +22416,7 @@
       <c r="AT655" s="3"/>
       <c r="AU655" s="3"/>
     </row>
-    <row r="656" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
@@ -22175,7 +22443,7 @@
       <c r="AT656" s="3"/>
       <c r="AU656" s="3"/>
     </row>
-    <row r="657" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
@@ -22202,7 +22470,7 @@
       <c r="AT657" s="3"/>
       <c r="AU657" s="3"/>
     </row>
-    <row r="658" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
@@ -22229,7 +22497,7 @@
       <c r="AT658" s="3"/>
       <c r="AU658" s="3"/>
     </row>
-    <row r="659" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
@@ -22256,7 +22524,7 @@
       <c r="AT659" s="3"/>
       <c r="AU659" s="3"/>
     </row>
-    <row r="660" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
@@ -22283,7 +22551,7 @@
       <c r="AT660" s="3"/>
       <c r="AU660" s="3"/>
     </row>
-    <row r="661" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
@@ -22310,7 +22578,7 @@
       <c r="AT661" s="3"/>
       <c r="AU661" s="3"/>
     </row>
-    <row r="662" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
@@ -22337,7 +22605,7 @@
       <c r="AT662" s="3"/>
       <c r="AU662" s="3"/>
     </row>
-    <row r="663" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
@@ -22364,7 +22632,7 @@
       <c r="AT663" s="3"/>
       <c r="AU663" s="3"/>
     </row>
-    <row r="664" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
@@ -22391,7 +22659,7 @@
       <c r="AT664" s="3"/>
       <c r="AU664" s="3"/>
     </row>
-    <row r="665" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
@@ -22418,7 +22686,7 @@
       <c r="AT665" s="3"/>
       <c r="AU665" s="3"/>
     </row>
-    <row r="666" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
@@ -22445,7 +22713,7 @@
       <c r="AT666" s="3"/>
       <c r="AU666" s="3"/>
     </row>
-    <row r="667" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
@@ -22472,7 +22740,7 @@
       <c r="AT667" s="3"/>
       <c r="AU667" s="3"/>
     </row>
-    <row r="668" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
@@ -22499,7 +22767,7 @@
       <c r="AT668" s="3"/>
       <c r="AU668" s="3"/>
     </row>
-    <row r="669" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
@@ -22526,7 +22794,7 @@
       <c r="AT669" s="3"/>
       <c r="AU669" s="3"/>
     </row>
-    <row r="670" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
@@ -22553,7 +22821,7 @@
       <c r="AT670" s="3"/>
       <c r="AU670" s="3"/>
     </row>
-    <row r="671" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
@@ -22580,7 +22848,7 @@
       <c r="AT671" s="3"/>
       <c r="AU671" s="3"/>
     </row>
-    <row r="672" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
@@ -22607,7 +22875,7 @@
       <c r="AT672" s="3"/>
       <c r="AU672" s="3"/>
     </row>
-    <row r="673" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
@@ -22634,7 +22902,7 @@
       <c r="AT673" s="3"/>
       <c r="AU673" s="3"/>
     </row>
-    <row r="674" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
@@ -22661,7 +22929,7 @@
       <c r="AT674" s="3"/>
       <c r="AU674" s="3"/>
     </row>
-    <row r="675" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
@@ -22688,7 +22956,7 @@
       <c r="AT675" s="3"/>
       <c r="AU675" s="3"/>
     </row>
-    <row r="676" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
@@ -22715,7 +22983,7 @@
       <c r="AT676" s="3"/>
       <c r="AU676" s="3"/>
     </row>
-    <row r="677" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
@@ -22742,7 +23010,7 @@
       <c r="AT677" s="3"/>
       <c r="AU677" s="3"/>
     </row>
-    <row r="678" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
@@ -22769,7 +23037,7 @@
       <c r="AT678" s="3"/>
       <c r="AU678" s="3"/>
     </row>
-    <row r="679" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
@@ -22796,7 +23064,7 @@
       <c r="AT679" s="3"/>
       <c r="AU679" s="3"/>
     </row>
-    <row r="680" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
@@ -22823,7 +23091,7 @@
       <c r="AT680" s="3"/>
       <c r="AU680" s="3"/>
     </row>
-    <row r="681" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
@@ -22850,7 +23118,7 @@
       <c r="AT681" s="3"/>
       <c r="AU681" s="3"/>
     </row>
-    <row r="682" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
@@ -22877,7 +23145,7 @@
       <c r="AT682" s="3"/>
       <c r="AU682" s="3"/>
     </row>
-    <row r="683" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
@@ -22904,7 +23172,7 @@
       <c r="AT683" s="3"/>
       <c r="AU683" s="3"/>
     </row>
-    <row r="684" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
@@ -22931,7 +23199,7 @@
       <c r="AT684" s="3"/>
       <c r="AU684" s="3"/>
     </row>
-    <row r="685" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
@@ -22958,7 +23226,7 @@
       <c r="AT685" s="3"/>
       <c r="AU685" s="3"/>
     </row>
-    <row r="686" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
@@ -22985,7 +23253,7 @@
       <c r="AT686" s="3"/>
       <c r="AU686" s="3"/>
     </row>
-    <row r="687" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
@@ -23012,7 +23280,7 @@
       <c r="AT687" s="3"/>
       <c r="AU687" s="3"/>
     </row>
-    <row r="688" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
@@ -23039,7 +23307,7 @@
       <c r="AT688" s="3"/>
       <c r="AU688" s="3"/>
     </row>
-    <row r="689" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
@@ -23066,7 +23334,7 @@
       <c r="AT689" s="3"/>
       <c r="AU689" s="3"/>
     </row>
-    <row r="690" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
@@ -23093,7 +23361,7 @@
       <c r="AT690" s="3"/>
       <c r="AU690" s="3"/>
     </row>
-    <row r="691" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
@@ -23120,7 +23388,7 @@
       <c r="AT691" s="3"/>
       <c r="AU691" s="3"/>
     </row>
-    <row r="692" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
@@ -23147,7 +23415,7 @@
       <c r="AT692" s="3"/>
       <c r="AU692" s="3"/>
     </row>
-    <row r="693" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
@@ -23174,7 +23442,7 @@
       <c r="AT693" s="3"/>
       <c r="AU693" s="3"/>
     </row>
-    <row r="694" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
@@ -23201,7 +23469,7 @@
       <c r="AT694" s="3"/>
       <c r="AU694" s="3"/>
     </row>
-    <row r="695" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
@@ -23228,7 +23496,7 @@
       <c r="AT695" s="3"/>
       <c r="AU695" s="3"/>
     </row>
-    <row r="696" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
@@ -23255,7 +23523,7 @@
       <c r="AT696" s="3"/>
       <c r="AU696" s="3"/>
     </row>
-    <row r="697" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
@@ -23282,7 +23550,7 @@
       <c r="AT697" s="3"/>
       <c r="AU697" s="3"/>
     </row>
-    <row r="698" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -23309,7 +23577,7 @@
       <c r="AT698" s="3"/>
       <c r="AU698" s="3"/>
     </row>
-    <row r="699" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -23336,7 +23604,7 @@
       <c r="AT699" s="3"/>
       <c r="AU699" s="3"/>
     </row>
-    <row r="700" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
@@ -23363,7 +23631,7 @@
       <c r="AT700" s="3"/>
       <c r="AU700" s="3"/>
     </row>
-    <row r="701" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -23390,7 +23658,7 @@
       <c r="AT701" s="3"/>
       <c r="AU701" s="3"/>
     </row>
-    <row r="702" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
@@ -23417,7 +23685,7 @@
       <c r="AT702" s="3"/>
       <c r="AU702" s="3"/>
     </row>
-    <row r="703" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
@@ -23444,7 +23712,7 @@
       <c r="AT703" s="3"/>
       <c r="AU703" s="3"/>
     </row>
-    <row r="704" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
@@ -23471,7 +23739,7 @@
       <c r="AT704" s="3"/>
       <c r="AU704" s="3"/>
     </row>
-    <row r="705" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -23498,7 +23766,7 @@
       <c r="AT705" s="3"/>
       <c r="AU705" s="3"/>
     </row>
-    <row r="706" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -23525,7 +23793,7 @@
       <c r="AT706" s="3"/>
       <c r="AU706" s="3"/>
     </row>
-    <row r="707" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
@@ -23552,7 +23820,7 @@
       <c r="AT707" s="3"/>
       <c r="AU707" s="3"/>
     </row>
-    <row r="708" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
@@ -23579,7 +23847,7 @@
       <c r="AT708" s="3"/>
       <c r="AU708" s="3"/>
     </row>
-    <row r="709" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -23606,7 +23874,7 @@
       <c r="AT709" s="3"/>
       <c r="AU709" s="3"/>
     </row>
-    <row r="710" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -23633,7 +23901,7 @@
       <c r="AT710" s="3"/>
       <c r="AU710" s="3"/>
     </row>
-    <row r="711" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -23660,7 +23928,7 @@
       <c r="AT711" s="3"/>
       <c r="AU711" s="3"/>
     </row>
-    <row r="712" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
@@ -23687,7 +23955,7 @@
       <c r="AT712" s="3"/>
       <c r="AU712" s="3"/>
     </row>
-    <row r="713" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -23714,7 +23982,7 @@
       <c r="AT713" s="3"/>
       <c r="AU713" s="3"/>
     </row>
-    <row r="714" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
@@ -23741,7 +24009,7 @@
       <c r="AT714" s="3"/>
       <c r="AU714" s="3"/>
     </row>
-    <row r="715" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -23768,7 +24036,7 @@
       <c r="AT715" s="3"/>
       <c r="AU715" s="3"/>
     </row>
-    <row r="716" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
@@ -23795,7 +24063,7 @@
       <c r="AT716" s="3"/>
       <c r="AU716" s="3"/>
     </row>
-    <row r="717" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
@@ -23822,7 +24090,7 @@
       <c r="AT717" s="3"/>
       <c r="AU717" s="3"/>
     </row>
-    <row r="718" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
@@ -23849,7 +24117,7 @@
       <c r="AT718" s="3"/>
       <c r="AU718" s="3"/>
     </row>
-    <row r="719" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -23876,7 +24144,7 @@
       <c r="AT719" s="3"/>
       <c r="AU719" s="3"/>
     </row>
-    <row r="720" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
@@ -23903,7 +24171,7 @@
       <c r="AT720" s="3"/>
       <c r="AU720" s="3"/>
     </row>
-    <row r="721" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
@@ -23930,7 +24198,7 @@
       <c r="AT721" s="3"/>
       <c r="AU721" s="3"/>
     </row>
-    <row r="722" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
@@ -23957,7 +24225,7 @@
       <c r="AT722" s="3"/>
       <c r="AU722" s="3"/>
     </row>
-    <row r="723" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
@@ -23984,7 +24252,7 @@
       <c r="AT723" s="3"/>
       <c r="AU723" s="3"/>
     </row>
-    <row r="724" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
@@ -24011,7 +24279,7 @@
       <c r="AT724" s="3"/>
       <c r="AU724" s="3"/>
     </row>
-    <row r="725" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
@@ -24038,7 +24306,7 @@
       <c r="AT725" s="3"/>
       <c r="AU725" s="3"/>
     </row>
-    <row r="726" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
@@ -24065,7 +24333,7 @@
       <c r="AT726" s="3"/>
       <c r="AU726" s="3"/>
     </row>
-    <row r="727" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
@@ -24092,7 +24360,7 @@
       <c r="AT727" s="3"/>
       <c r="AU727" s="3"/>
     </row>
-    <row r="728" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
@@ -24119,7 +24387,7 @@
       <c r="AT728" s="3"/>
       <c r="AU728" s="3"/>
     </row>
-    <row r="729" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
@@ -24146,7 +24414,7 @@
       <c r="AT729" s="3"/>
       <c r="AU729" s="3"/>
     </row>
-    <row r="730" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
@@ -24173,7 +24441,7 @@
       <c r="AT730" s="3"/>
       <c r="AU730" s="3"/>
     </row>
-    <row r="731" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
@@ -24200,7 +24468,7 @@
       <c r="AT731" s="3"/>
       <c r="AU731" s="3"/>
     </row>
-    <row r="732" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
@@ -24227,7 +24495,7 @@
       <c r="AT732" s="3"/>
       <c r="AU732" s="3"/>
     </row>
-    <row r="733" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
@@ -24254,7 +24522,7 @@
       <c r="AT733" s="3"/>
       <c r="AU733" s="3"/>
     </row>
-    <row r="734" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
@@ -24281,7 +24549,7 @@
       <c r="AT734" s="3"/>
       <c r="AU734" s="3"/>
     </row>
-    <row r="735" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
@@ -24308,7 +24576,7 @@
       <c r="AT735" s="3"/>
       <c r="AU735" s="3"/>
     </row>
-    <row r="736" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
@@ -24335,7 +24603,7 @@
       <c r="AT736" s="3"/>
       <c r="AU736" s="3"/>
     </row>
-    <row r="737" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
@@ -24362,7 +24630,7 @@
       <c r="AT737" s="3"/>
       <c r="AU737" s="3"/>
     </row>
-    <row r="738" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
@@ -24389,7 +24657,7 @@
       <c r="AT738" s="3"/>
       <c r="AU738" s="3"/>
     </row>
-    <row r="739" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
@@ -24416,7 +24684,7 @@
       <c r="AT739" s="3"/>
       <c r="AU739" s="3"/>
     </row>
-    <row r="740" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
@@ -24443,7 +24711,7 @@
       <c r="AT740" s="3"/>
       <c r="AU740" s="3"/>
     </row>
-    <row r="741" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
@@ -24470,7 +24738,7 @@
       <c r="AT741" s="3"/>
       <c r="AU741" s="3"/>
     </row>
-    <row r="742" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
@@ -24497,7 +24765,7 @@
       <c r="AT742" s="3"/>
       <c r="AU742" s="3"/>
     </row>
-    <row r="743" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
@@ -24524,7 +24792,7 @@
       <c r="AT743" s="3"/>
       <c r="AU743" s="3"/>
     </row>
-    <row r="744" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
@@ -24551,7 +24819,7 @@
       <c r="AT744" s="3"/>
       <c r="AU744" s="3"/>
     </row>
-    <row r="745" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
@@ -24578,7 +24846,7 @@
       <c r="AT745" s="3"/>
       <c r="AU745" s="3"/>
     </row>
-    <row r="746" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
@@ -24605,7 +24873,7 @@
       <c r="AT746" s="3"/>
       <c r="AU746" s="3"/>
     </row>
-    <row r="747" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
@@ -24632,7 +24900,7 @@
       <c r="AT747" s="3"/>
       <c r="AU747" s="3"/>
     </row>
-    <row r="748" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
@@ -24659,7 +24927,7 @@
       <c r="AT748" s="3"/>
       <c r="AU748" s="3"/>
     </row>
-    <row r="749" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
@@ -24686,7 +24954,7 @@
       <c r="AT749" s="3"/>
       <c r="AU749" s="3"/>
     </row>
-    <row r="750" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
@@ -24713,7 +24981,7 @@
       <c r="AT750" s="3"/>
       <c r="AU750" s="3"/>
     </row>
-    <row r="751" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
@@ -24740,7 +25008,7 @@
       <c r="AT751" s="3"/>
       <c r="AU751" s="3"/>
     </row>
-    <row r="752" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
@@ -24767,7 +25035,7 @@
       <c r="AT752" s="3"/>
       <c r="AU752" s="3"/>
     </row>
-    <row r="753" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
@@ -24794,7 +25062,7 @@
       <c r="AT753" s="3"/>
       <c r="AU753" s="3"/>
     </row>
-    <row r="754" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
@@ -24821,7 +25089,7 @@
       <c r="AT754" s="3"/>
       <c r="AU754" s="3"/>
     </row>
-    <row r="755" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
@@ -24848,7 +25116,7 @@
       <c r="AT755" s="3"/>
       <c r="AU755" s="3"/>
     </row>
-    <row r="756" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
@@ -24875,7 +25143,7 @@
       <c r="AT756" s="3"/>
       <c r="AU756" s="3"/>
     </row>
-    <row r="757" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
@@ -24902,7 +25170,7 @@
       <c r="AT757" s="3"/>
       <c r="AU757" s="3"/>
     </row>
-    <row r="758" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
@@ -24929,7 +25197,7 @@
       <c r="AT758" s="3"/>
       <c r="AU758" s="3"/>
     </row>
-    <row r="759" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
@@ -24956,7 +25224,7 @@
       <c r="AT759" s="3"/>
       <c r="AU759" s="3"/>
     </row>
-    <row r="760" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
@@ -24983,7 +25251,7 @@
       <c r="AT760" s="3"/>
       <c r="AU760" s="3"/>
     </row>
-    <row r="761" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
@@ -25010,7 +25278,7 @@
       <c r="AT761" s="3"/>
       <c r="AU761" s="3"/>
     </row>
-    <row r="762" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
@@ -25037,7 +25305,7 @@
       <c r="AT762" s="3"/>
       <c r="AU762" s="3"/>
     </row>
-    <row r="763" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
@@ -25064,7 +25332,7 @@
       <c r="AT763" s="3"/>
       <c r="AU763" s="3"/>
     </row>
-    <row r="764" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
@@ -25091,7 +25359,7 @@
       <c r="AT764" s="3"/>
       <c r="AU764" s="3"/>
     </row>
-    <row r="765" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
@@ -25118,7 +25386,7 @@
       <c r="AT765" s="3"/>
       <c r="AU765" s="3"/>
     </row>
-    <row r="766" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
@@ -25145,7 +25413,7 @@
       <c r="AT766" s="3"/>
       <c r="AU766" s="3"/>
     </row>
-    <row r="767" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
@@ -25172,7 +25440,7 @@
       <c r="AT767" s="3"/>
       <c r="AU767" s="3"/>
     </row>
-    <row r="768" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
@@ -25199,7 +25467,7 @@
       <c r="AT768" s="3"/>
       <c r="AU768" s="3"/>
     </row>
-    <row r="769" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
@@ -25226,7 +25494,7 @@
       <c r="AT769" s="3"/>
       <c r="AU769" s="3"/>
     </row>
-    <row r="770" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
@@ -25253,7 +25521,7 @@
       <c r="AT770" s="3"/>
       <c r="AU770" s="3"/>
     </row>
-    <row r="771" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
@@ -25280,7 +25548,7 @@
       <c r="AT771" s="3"/>
       <c r="AU771" s="3"/>
     </row>
-    <row r="772" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
@@ -25307,7 +25575,7 @@
       <c r="AT772" s="3"/>
       <c r="AU772" s="3"/>
     </row>
-    <row r="773" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
@@ -25334,7 +25602,7 @@
       <c r="AT773" s="3"/>
       <c r="AU773" s="3"/>
     </row>
-    <row r="774" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
@@ -25361,7 +25629,7 @@
       <c r="AT774" s="3"/>
       <c r="AU774" s="3"/>
     </row>
-    <row r="775" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
@@ -25388,7 +25656,7 @@
       <c r="AT775" s="3"/>
       <c r="AU775" s="3"/>
     </row>
-    <row r="776" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
@@ -25415,7 +25683,7 @@
       <c r="AT776" s="3"/>
       <c r="AU776" s="3"/>
     </row>
-    <row r="777" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
@@ -25442,7 +25710,7 @@
       <c r="AT777" s="3"/>
       <c r="AU777" s="3"/>
     </row>
-    <row r="778" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
@@ -25469,7 +25737,7 @@
       <c r="AT778" s="3"/>
       <c r="AU778" s="3"/>
     </row>
-    <row r="779" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
@@ -25496,7 +25764,7 @@
       <c r="AT779" s="3"/>
       <c r="AU779" s="3"/>
     </row>
-    <row r="780" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
@@ -25523,7 +25791,7 @@
       <c r="AT780" s="3"/>
       <c r="AU780" s="3"/>
     </row>
-    <row r="781" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
@@ -25550,7 +25818,7 @@
       <c r="AT781" s="3"/>
       <c r="AU781" s="3"/>
     </row>
-    <row r="782" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
@@ -25577,7 +25845,7 @@
       <c r="AT782" s="3"/>
       <c r="AU782" s="3"/>
     </row>
-    <row r="783" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
@@ -25604,7 +25872,7 @@
       <c r="AT783" s="3"/>
       <c r="AU783" s="3"/>
     </row>
-    <row r="784" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
@@ -25631,7 +25899,7 @@
       <c r="AT784" s="3"/>
       <c r="AU784" s="3"/>
     </row>
-    <row r="785" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -25658,7 +25926,7 @@
       <c r="AT785" s="3"/>
       <c r="AU785" s="3"/>
     </row>
-    <row r="786" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
@@ -25685,7 +25953,7 @@
       <c r="AT786" s="3"/>
       <c r="AU786" s="3"/>
     </row>
-    <row r="787" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
@@ -25712,7 +25980,7 @@
       <c r="AT787" s="3"/>
       <c r="AU787" s="3"/>
     </row>
-    <row r="788" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
@@ -25739,7 +26007,7 @@
       <c r="AT788" s="3"/>
       <c r="AU788" s="3"/>
     </row>
-    <row r="789" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
@@ -25766,7 +26034,7 @@
       <c r="AT789" s="3"/>
       <c r="AU789" s="3"/>
     </row>
-    <row r="790" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
@@ -25793,7 +26061,7 @@
       <c r="AT790" s="3"/>
       <c r="AU790" s="3"/>
     </row>
-    <row r="791" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
@@ -25820,7 +26088,7 @@
       <c r="AT791" s="3"/>
       <c r="AU791" s="3"/>
     </row>
-    <row r="792" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
@@ -25847,7 +26115,7 @@
       <c r="AT792" s="3"/>
       <c r="AU792" s="3"/>
     </row>
-    <row r="793" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
@@ -25874,7 +26142,7 @@
       <c r="AT793" s="3"/>
       <c r="AU793" s="3"/>
     </row>
-    <row r="794" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
@@ -25901,7 +26169,7 @@
       <c r="AT794" s="3"/>
       <c r="AU794" s="3"/>
     </row>
-    <row r="795" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -25928,7 +26196,7 @@
       <c r="AT795" s="3"/>
       <c r="AU795" s="3"/>
     </row>
-    <row r="796" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
@@ -25955,7 +26223,7 @@
       <c r="AT796" s="3"/>
       <c r="AU796" s="3"/>
     </row>
-    <row r="797" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -25982,7 +26250,7 @@
       <c r="AT797" s="3"/>
       <c r="AU797" s="3"/>
     </row>
-    <row r="798" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
@@ -26009,7 +26277,7 @@
       <c r="AT798" s="3"/>
       <c r="AU798" s="3"/>
     </row>
-    <row r="799" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -26036,7 +26304,7 @@
       <c r="AT799" s="3"/>
       <c r="AU799" s="3"/>
     </row>
-    <row r="800" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
@@ -26063,7 +26331,7 @@
       <c r="AT800" s="3"/>
       <c r="AU800" s="3"/>
     </row>
-    <row r="801" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
@@ -26090,7 +26358,7 @@
       <c r="AT801" s="3"/>
       <c r="AU801" s="3"/>
     </row>
-    <row r="802" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
@@ -26117,7 +26385,7 @@
       <c r="AT802" s="3"/>
       <c r="AU802" s="3"/>
     </row>
-    <row r="803" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
@@ -26144,7 +26412,7 @@
       <c r="AT803" s="3"/>
       <c r="AU803" s="3"/>
     </row>
-    <row r="804" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
@@ -26171,7 +26439,7 @@
       <c r="AT804" s="3"/>
       <c r="AU804" s="3"/>
     </row>
-    <row r="805" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
@@ -26198,7 +26466,7 @@
       <c r="AT805" s="3"/>
       <c r="AU805" s="3"/>
     </row>
-    <row r="806" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -26225,7 +26493,7 @@
       <c r="AT806" s="3"/>
       <c r="AU806" s="3"/>
     </row>
-    <row r="807" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
@@ -26252,7 +26520,7 @@
       <c r="AT807" s="3"/>
       <c r="AU807" s="3"/>
     </row>
-    <row r="808" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
@@ -26279,7 +26547,7 @@
       <c r="AT808" s="3"/>
       <c r="AU808" s="3"/>
     </row>
-    <row r="809" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
@@ -26306,7 +26574,7 @@
       <c r="AT809" s="3"/>
       <c r="AU809" s="3"/>
     </row>
-    <row r="810" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
@@ -26333,7 +26601,7 @@
       <c r="AT810" s="3"/>
       <c r="AU810" s="3"/>
     </row>
-    <row r="811" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
@@ -26360,7 +26628,7 @@
       <c r="AT811" s="3"/>
       <c r="AU811" s="3"/>
     </row>
-    <row r="812" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
@@ -26387,7 +26655,7 @@
       <c r="AT812" s="3"/>
       <c r="AU812" s="3"/>
     </row>
-    <row r="813" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
@@ -26414,7 +26682,7 @@
       <c r="AT813" s="3"/>
       <c r="AU813" s="3"/>
     </row>
-    <row r="814" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
@@ -26441,7 +26709,7 @@
       <c r="AT814" s="3"/>
       <c r="AU814" s="3"/>
     </row>
-    <row r="815" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
@@ -26468,7 +26736,7 @@
       <c r="AT815" s="3"/>
       <c r="AU815" s="3"/>
     </row>
-    <row r="816" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
@@ -26495,7 +26763,7 @@
       <c r="AT816" s="3"/>
       <c r="AU816" s="3"/>
     </row>
-    <row r="817" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
@@ -26522,7 +26790,7 @@
       <c r="AT817" s="3"/>
       <c r="AU817" s="3"/>
     </row>
-    <row r="818" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
@@ -26549,7 +26817,7 @@
       <c r="AT818" s="3"/>
       <c r="AU818" s="3"/>
     </row>
-    <row r="819" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
@@ -26576,7 +26844,7 @@
       <c r="AT819" s="3"/>
       <c r="AU819" s="3"/>
     </row>
-    <row r="820" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
@@ -26603,7 +26871,7 @@
       <c r="AT820" s="3"/>
       <c r="AU820" s="3"/>
     </row>
-    <row r="821" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
@@ -26630,7 +26898,7 @@
       <c r="AT821" s="3"/>
       <c r="AU821" s="3"/>
     </row>
-    <row r="822" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
@@ -26657,7 +26925,7 @@
       <c r="AT822" s="3"/>
       <c r="AU822" s="3"/>
     </row>
-    <row r="823" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
@@ -26684,7 +26952,7 @@
       <c r="AT823" s="3"/>
       <c r="AU823" s="3"/>
     </row>
-    <row r="824" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
@@ -26711,7 +26979,7 @@
       <c r="AT824" s="3"/>
       <c r="AU824" s="3"/>
     </row>
-    <row r="825" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
@@ -26738,7 +27006,7 @@
       <c r="AT825" s="3"/>
       <c r="AU825" s="3"/>
     </row>
-    <row r="826" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
@@ -26765,7 +27033,7 @@
       <c r="AT826" s="3"/>
       <c r="AU826" s="3"/>
     </row>
-    <row r="827" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
@@ -26792,7 +27060,7 @@
       <c r="AT827" s="3"/>
       <c r="AU827" s="3"/>
     </row>
-    <row r="828" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
@@ -26819,7 +27087,7 @@
       <c r="AT828" s="3"/>
       <c r="AU828" s="3"/>
     </row>
-    <row r="829" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
@@ -26846,7 +27114,7 @@
       <c r="AT829" s="3"/>
       <c r="AU829" s="3"/>
     </row>
-    <row r="830" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
@@ -26873,7 +27141,7 @@
       <c r="AT830" s="3"/>
       <c r="AU830" s="3"/>
     </row>
-    <row r="831" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
@@ -26900,7 +27168,7 @@
       <c r="AT831" s="3"/>
       <c r="AU831" s="3"/>
     </row>
-    <row r="832" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
@@ -26927,7 +27195,7 @@
       <c r="AT832" s="3"/>
       <c r="AU832" s="3"/>
     </row>
-    <row r="833" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
@@ -26954,7 +27222,7 @@
       <c r="AT833" s="3"/>
       <c r="AU833" s="3"/>
     </row>
-    <row r="834" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
@@ -26981,7 +27249,7 @@
       <c r="AT834" s="3"/>
       <c r="AU834" s="3"/>
     </row>
-    <row r="835" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
@@ -27008,7 +27276,7 @@
       <c r="AT835" s="3"/>
       <c r="AU835" s="3"/>
     </row>
-    <row r="836" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
@@ -27035,7 +27303,7 @@
       <c r="AT836" s="3"/>
       <c r="AU836" s="3"/>
     </row>
-    <row r="837" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
@@ -27062,7 +27330,7 @@
       <c r="AT837" s="3"/>
       <c r="AU837" s="3"/>
     </row>
-    <row r="838" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
@@ -27089,7 +27357,7 @@
       <c r="AT838" s="3"/>
       <c r="AU838" s="3"/>
     </row>
-    <row r="839" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
@@ -27116,7 +27384,7 @@
       <c r="AT839" s="3"/>
       <c r="AU839" s="3"/>
     </row>
-    <row r="840" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
@@ -27143,7 +27411,7 @@
       <c r="AT840" s="3"/>
       <c r="AU840" s="3"/>
     </row>
-    <row r="841" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
@@ -27170,7 +27438,7 @@
       <c r="AT841" s="3"/>
       <c r="AU841" s="3"/>
     </row>
-    <row r="842" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
@@ -27197,7 +27465,7 @@
       <c r="AT842" s="3"/>
       <c r="AU842" s="3"/>
     </row>
-    <row r="843" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
@@ -27224,7 +27492,7 @@
       <c r="AT843" s="3"/>
       <c r="AU843" s="3"/>
     </row>
-    <row r="844" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
@@ -27251,7 +27519,7 @@
       <c r="AT844" s="3"/>
       <c r="AU844" s="3"/>
     </row>
-    <row r="845" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
@@ -27278,7 +27546,7 @@
       <c r="AT845" s="3"/>
       <c r="AU845" s="3"/>
     </row>
-    <row r="846" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
@@ -27305,7 +27573,7 @@
       <c r="AT846" s="3"/>
       <c r="AU846" s="3"/>
     </row>
-    <row r="847" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
@@ -27332,7 +27600,7 @@
       <c r="AT847" s="3"/>
       <c r="AU847" s="3"/>
     </row>
-    <row r="848" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
@@ -27359,7 +27627,7 @@
       <c r="AT848" s="3"/>
       <c r="AU848" s="3"/>
     </row>
-    <row r="849" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
@@ -27386,7 +27654,7 @@
       <c r="AT849" s="3"/>
       <c r="AU849" s="3"/>
     </row>
-    <row r="850" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
@@ -27413,7 +27681,7 @@
       <c r="AT850" s="3"/>
       <c r="AU850" s="3"/>
     </row>
-    <row r="851" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
@@ -27440,7 +27708,7 @@
       <c r="AT851" s="3"/>
       <c r="AU851" s="3"/>
     </row>
-    <row r="852" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
@@ -27467,7 +27735,7 @@
       <c r="AT852" s="3"/>
       <c r="AU852" s="3"/>
     </row>
-    <row r="853" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
@@ -27494,7 +27762,7 @@
       <c r="AT853" s="3"/>
       <c r="AU853" s="3"/>
     </row>
-    <row r="854" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
@@ -27521,7 +27789,7 @@
       <c r="AT854" s="3"/>
       <c r="AU854" s="3"/>
     </row>
-    <row r="855" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
@@ -27548,7 +27816,7 @@
       <c r="AT855" s="3"/>
       <c r="AU855" s="3"/>
     </row>
-    <row r="856" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
@@ -27575,7 +27843,7 @@
       <c r="AT856" s="3"/>
       <c r="AU856" s="3"/>
     </row>
-    <row r="857" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
@@ -27602,7 +27870,7 @@
       <c r="AT857" s="3"/>
       <c r="AU857" s="3"/>
     </row>
-    <row r="858" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
@@ -27629,7 +27897,7 @@
       <c r="AT858" s="3"/>
       <c r="AU858" s="3"/>
     </row>
-    <row r="859" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
@@ -27656,7 +27924,7 @@
       <c r="AT859" s="3"/>
       <c r="AU859" s="3"/>
     </row>
-    <row r="860" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
@@ -27683,7 +27951,7 @@
       <c r="AT860" s="3"/>
       <c r="AU860" s="3"/>
     </row>
-    <row r="861" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
@@ -27710,7 +27978,7 @@
       <c r="AT861" s="3"/>
       <c r="AU861" s="3"/>
     </row>
-    <row r="862" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
@@ -27737,7 +28005,7 @@
       <c r="AT862" s="3"/>
       <c r="AU862" s="3"/>
     </row>
-    <row r="863" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
@@ -27764,7 +28032,7 @@
       <c r="AT863" s="3"/>
       <c r="AU863" s="3"/>
     </row>
-    <row r="864" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
@@ -27791,7 +28059,7 @@
       <c r="AT864" s="3"/>
       <c r="AU864" s="3"/>
     </row>
-    <row r="865" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
@@ -27818,7 +28086,7 @@
       <c r="AT865" s="3"/>
       <c r="AU865" s="3"/>
     </row>
-    <row r="866" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
@@ -27845,7 +28113,7 @@
       <c r="AT866" s="3"/>
       <c r="AU866" s="3"/>
     </row>
-    <row r="867" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
@@ -27872,7 +28140,7 @@
       <c r="AT867" s="3"/>
       <c r="AU867" s="3"/>
     </row>
-    <row r="868" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
@@ -27899,7 +28167,7 @@
       <c r="AT868" s="3"/>
       <c r="AU868" s="3"/>
     </row>
-    <row r="869" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
@@ -27926,7 +28194,7 @@
       <c r="AT869" s="3"/>
       <c r="AU869" s="3"/>
     </row>
-    <row r="870" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
@@ -27953,7 +28221,7 @@
       <c r="AT870" s="3"/>
       <c r="AU870" s="3"/>
     </row>
-    <row r="871" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
@@ -27980,7 +28248,7 @@
       <c r="AT871" s="3"/>
       <c r="AU871" s="3"/>
     </row>
-    <row r="872" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
@@ -28007,7 +28275,7 @@
       <c r="AT872" s="3"/>
       <c r="AU872" s="3"/>
     </row>
-    <row r="873" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
@@ -28034,7 +28302,7 @@
       <c r="AT873" s="3"/>
       <c r="AU873" s="3"/>
     </row>
-    <row r="874" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
@@ -28061,7 +28329,7 @@
       <c r="AT874" s="3"/>
       <c r="AU874" s="3"/>
     </row>
-    <row r="875" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
@@ -28088,7 +28356,7 @@
       <c r="AT875" s="3"/>
       <c r="AU875" s="3"/>
     </row>
-    <row r="876" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
@@ -28115,7 +28383,7 @@
       <c r="AT876" s="3"/>
       <c r="AU876" s="3"/>
     </row>
-    <row r="877" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
@@ -28142,7 +28410,7 @@
       <c r="AT877" s="3"/>
       <c r="AU877" s="3"/>
     </row>
-    <row r="878" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
@@ -28169,7 +28437,7 @@
       <c r="AT878" s="3"/>
       <c r="AU878" s="3"/>
     </row>
-    <row r="879" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
@@ -28196,7 +28464,7 @@
       <c r="AT879" s="3"/>
       <c r="AU879" s="3"/>
     </row>
-    <row r="880" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
@@ -28223,7 +28491,7 @@
       <c r="AT880" s="3"/>
       <c r="AU880" s="3"/>
     </row>
-    <row r="881" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
@@ -28250,7 +28518,7 @@
       <c r="AT881" s="3"/>
       <c r="AU881" s="3"/>
     </row>
-    <row r="882" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
@@ -28277,7 +28545,7 @@
       <c r="AT882" s="3"/>
       <c r="AU882" s="3"/>
     </row>
-    <row r="883" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
@@ -28304,7 +28572,7 @@
       <c r="AT883" s="3"/>
       <c r="AU883" s="3"/>
     </row>
-    <row r="884" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
@@ -28331,7 +28599,7 @@
       <c r="AT884" s="3"/>
       <c r="AU884" s="3"/>
     </row>
-    <row r="885" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
@@ -28358,7 +28626,7 @@
       <c r="AT885" s="3"/>
       <c r="AU885" s="3"/>
     </row>
-    <row r="886" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
@@ -28385,7 +28653,7 @@
       <c r="AT886" s="3"/>
       <c r="AU886" s="3"/>
     </row>
-    <row r="887" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
@@ -28412,7 +28680,7 @@
       <c r="AT887" s="3"/>
       <c r="AU887" s="3"/>
     </row>
-    <row r="888" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
@@ -28439,7 +28707,7 @@
       <c r="AT888" s="3"/>
       <c r="AU888" s="3"/>
     </row>
-    <row r="889" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
@@ -28466,7 +28734,7 @@
       <c r="AT889" s="3"/>
       <c r="AU889" s="3"/>
     </row>
-    <row r="890" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
@@ -28493,7 +28761,7 @@
       <c r="AT890" s="3"/>
       <c r="AU890" s="3"/>
     </row>
-    <row r="891" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
@@ -28520,7 +28788,7 @@
       <c r="AT891" s="3"/>
       <c r="AU891" s="3"/>
     </row>
-    <row r="892" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
@@ -28547,7 +28815,7 @@
       <c r="AT892" s="3"/>
       <c r="AU892" s="3"/>
     </row>
-    <row r="893" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
@@ -28574,7 +28842,7 @@
       <c r="AT893" s="3"/>
       <c r="AU893" s="3"/>
     </row>
-    <row r="894" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
@@ -28601,7 +28869,7 @@
       <c r="AT894" s="3"/>
       <c r="AU894" s="3"/>
     </row>
-    <row r="895" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
@@ -28628,7 +28896,7 @@
       <c r="AT895" s="3"/>
       <c r="AU895" s="3"/>
     </row>
-    <row r="896" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
@@ -28655,7 +28923,7 @@
       <c r="AT896" s="3"/>
       <c r="AU896" s="3"/>
     </row>
-    <row r="897" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
@@ -28682,7 +28950,7 @@
       <c r="AT897" s="3"/>
       <c r="AU897" s="3"/>
     </row>
-    <row r="898" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
@@ -28709,7 +28977,7 @@
       <c r="AT898" s="3"/>
       <c r="AU898" s="3"/>
     </row>
-    <row r="899" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
@@ -28736,7 +29004,7 @@
       <c r="AT899" s="3"/>
       <c r="AU899" s="3"/>
     </row>
-    <row r="900" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
@@ -28763,7 +29031,7 @@
       <c r="AT900" s="3"/>
       <c r="AU900" s="3"/>
     </row>
-    <row r="901" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
@@ -28790,7 +29058,7 @@
       <c r="AT901" s="3"/>
       <c r="AU901" s="3"/>
     </row>
-    <row r="902" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
@@ -28817,7 +29085,7 @@
       <c r="AT902" s="3"/>
       <c r="AU902" s="3"/>
     </row>
-    <row r="903" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
@@ -28844,7 +29112,7 @@
       <c r="AT903" s="3"/>
       <c r="AU903" s="3"/>
     </row>
-    <row r="904" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
@@ -28871,7 +29139,7 @@
       <c r="AT904" s="3"/>
       <c r="AU904" s="3"/>
     </row>
-    <row r="905" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
@@ -28898,7 +29166,7 @@
       <c r="AT905" s="3"/>
       <c r="AU905" s="3"/>
     </row>
-    <row r="906" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
@@ -28925,7 +29193,7 @@
       <c r="AT906" s="3"/>
       <c r="AU906" s="3"/>
     </row>
-    <row r="907" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
@@ -28952,7 +29220,7 @@
       <c r="AT907" s="3"/>
       <c r="AU907" s="3"/>
     </row>
-    <row r="908" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
@@ -28979,7 +29247,7 @@
       <c r="AT908" s="3"/>
       <c r="AU908" s="3"/>
     </row>
-    <row r="909" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
@@ -29006,7 +29274,7 @@
       <c r="AT909" s="3"/>
       <c r="AU909" s="3"/>
     </row>
-    <row r="910" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
@@ -29033,7 +29301,7 @@
       <c r="AT910" s="3"/>
       <c r="AU910" s="3"/>
     </row>
-    <row r="911" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
@@ -29060,7 +29328,7 @@
       <c r="AT911" s="3"/>
       <c r="AU911" s="3"/>
     </row>
-    <row r="912" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
@@ -29087,7 +29355,7 @@
       <c r="AT912" s="3"/>
       <c r="AU912" s="3"/>
     </row>
-    <row r="913" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
@@ -29114,7 +29382,7 @@
       <c r="AT913" s="3"/>
       <c r="AU913" s="3"/>
     </row>
-    <row r="914" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
@@ -29141,7 +29409,7 @@
       <c r="AT914" s="3"/>
       <c r="AU914" s="3"/>
     </row>
-    <row r="915" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
@@ -29168,7 +29436,7 @@
       <c r="AT915" s="3"/>
       <c r="AU915" s="3"/>
     </row>
-    <row r="916" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
@@ -29195,7 +29463,7 @@
       <c r="AT916" s="3"/>
       <c r="AU916" s="3"/>
     </row>
-    <row r="917" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
@@ -29222,7 +29490,7 @@
       <c r="AT917" s="3"/>
       <c r="AU917" s="3"/>
     </row>
-    <row r="918" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
@@ -29249,7 +29517,7 @@
       <c r="AT918" s="3"/>
       <c r="AU918" s="3"/>
     </row>
-    <row r="919" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
@@ -29276,7 +29544,7 @@
       <c r="AT919" s="3"/>
       <c r="AU919" s="3"/>
     </row>
-    <row r="920" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
@@ -29303,7 +29571,7 @@
       <c r="AT920" s="3"/>
       <c r="AU920" s="3"/>
     </row>
-    <row r="921" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
@@ -29330,7 +29598,7 @@
       <c r="AT921" s="3"/>
       <c r="AU921" s="3"/>
     </row>
-    <row r="922" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
@@ -29357,7 +29625,7 @@
       <c r="AT922" s="3"/>
       <c r="AU922" s="3"/>
     </row>
-    <row r="923" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
@@ -29384,7 +29652,7 @@
       <c r="AT923" s="3"/>
       <c r="AU923" s="3"/>
     </row>
-    <row r="924" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
@@ -29411,7 +29679,7 @@
       <c r="AT924" s="3"/>
       <c r="AU924" s="3"/>
     </row>
-    <row r="925" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
@@ -29438,7 +29706,7 @@
       <c r="AT925" s="3"/>
       <c r="AU925" s="3"/>
     </row>
-    <row r="926" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
@@ -29465,7 +29733,7 @@
       <c r="AT926" s="3"/>
       <c r="AU926" s="3"/>
     </row>
-    <row r="927" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
@@ -29492,7 +29760,7 @@
       <c r="AT927" s="3"/>
       <c r="AU927" s="3"/>
     </row>
-    <row r="928" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
@@ -29519,7 +29787,7 @@
       <c r="AT928" s="3"/>
       <c r="AU928" s="3"/>
     </row>
-    <row r="929" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
@@ -29546,7 +29814,7 @@
       <c r="AT929" s="3"/>
       <c r="AU929" s="3"/>
     </row>
-    <row r="930" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
@@ -29573,7 +29841,7 @@
       <c r="AT930" s="3"/>
       <c r="AU930" s="3"/>
     </row>
-    <row r="931" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
@@ -29600,7 +29868,7 @@
       <c r="AT931" s="3"/>
       <c r="AU931" s="3"/>
     </row>
-    <row r="932" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
@@ -29627,7 +29895,7 @@
       <c r="AT932" s="3"/>
       <c r="AU932" s="3"/>
     </row>
-    <row r="933" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
@@ -29654,7 +29922,7 @@
       <c r="AT933" s="3"/>
       <c r="AU933" s="3"/>
     </row>
-    <row r="934" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
@@ -29681,7 +29949,7 @@
       <c r="AT934" s="3"/>
       <c r="AU934" s="3"/>
     </row>
-    <row r="935" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
@@ -29708,7 +29976,7 @@
       <c r="AT935" s="3"/>
       <c r="AU935" s="3"/>
     </row>
-    <row r="936" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
@@ -29735,7 +30003,7 @@
       <c r="AT936" s="3"/>
       <c r="AU936" s="3"/>
     </row>
-    <row r="937" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
@@ -29762,7 +30030,7 @@
       <c r="AT937" s="3"/>
       <c r="AU937" s="3"/>
     </row>
-    <row r="938" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
@@ -29789,7 +30057,7 @@
       <c r="AT938" s="3"/>
       <c r="AU938" s="3"/>
     </row>
-    <row r="939" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
@@ -29816,7 +30084,7 @@
       <c r="AT939" s="3"/>
       <c r="AU939" s="3"/>
     </row>
-    <row r="940" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
@@ -29843,7 +30111,7 @@
       <c r="AT940" s="3"/>
       <c r="AU940" s="3"/>
     </row>
-    <row r="941" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
@@ -29870,7 +30138,7 @@
       <c r="AT941" s="3"/>
       <c r="AU941" s="3"/>
     </row>
-    <row r="942" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
@@ -29897,7 +30165,7 @@
       <c r="AT942" s="3"/>
       <c r="AU942" s="3"/>
     </row>
-    <row r="943" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
@@ -29924,7 +30192,7 @@
       <c r="AT943" s="3"/>
       <c r="AU943" s="3"/>
     </row>
-    <row r="944" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
@@ -29951,7 +30219,7 @@
       <c r="AT944" s="3"/>
       <c r="AU944" s="3"/>
     </row>
-    <row r="945" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
@@ -29978,7 +30246,7 @@
       <c r="AT945" s="3"/>
       <c r="AU945" s="3"/>
     </row>
-    <row r="946" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
@@ -30005,7 +30273,7 @@
       <c r="AT946" s="3"/>
       <c r="AU946" s="3"/>
     </row>
-    <row r="947" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
@@ -30032,7 +30300,7 @@
       <c r="AT947" s="3"/>
       <c r="AU947" s="3"/>
     </row>
-    <row r="948" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
@@ -30059,7 +30327,7 @@
       <c r="AT948" s="3"/>
       <c r="AU948" s="3"/>
     </row>
-    <row r="949" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
@@ -30086,7 +30354,7 @@
       <c r="AT949" s="3"/>
       <c r="AU949" s="3"/>
     </row>
-    <row r="950" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
@@ -30113,7 +30381,7 @@
       <c r="AT950" s="3"/>
       <c r="AU950" s="3"/>
     </row>
-    <row r="951" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
@@ -30140,7 +30408,7 @@
       <c r="AT951" s="3"/>
       <c r="AU951" s="3"/>
     </row>
-    <row r="952" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
@@ -30167,7 +30435,7 @@
       <c r="AT952" s="3"/>
       <c r="AU952" s="3"/>
     </row>
-    <row r="953" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
@@ -30194,7 +30462,7 @@
       <c r="AT953" s="3"/>
       <c r="AU953" s="3"/>
     </row>
-    <row r="954" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
@@ -30221,7 +30489,7 @@
       <c r="AT954" s="3"/>
       <c r="AU954" s="3"/>
     </row>
-    <row r="955" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
@@ -30248,7 +30516,7 @@
       <c r="AT955" s="3"/>
       <c r="AU955" s="3"/>
     </row>
-    <row r="956" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
@@ -30275,7 +30543,7 @@
       <c r="AT956" s="3"/>
       <c r="AU956" s="3"/>
     </row>
-    <row r="957" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
@@ -30302,7 +30570,7 @@
       <c r="AT957" s="3"/>
       <c r="AU957" s="3"/>
     </row>
-    <row r="958" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
@@ -30329,7 +30597,7 @@
       <c r="AT958" s="3"/>
       <c r="AU958" s="3"/>
     </row>
-    <row r="959" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
@@ -30356,7 +30624,7 @@
       <c r="AT959" s="3"/>
       <c r="AU959" s="3"/>
     </row>
-    <row r="960" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
@@ -30383,7 +30651,7 @@
       <c r="AT960" s="3"/>
       <c r="AU960" s="3"/>
     </row>
-    <row r="961" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
@@ -30410,7 +30678,7 @@
       <c r="AT961" s="3"/>
       <c r="AU961" s="3"/>
     </row>
-    <row r="962" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
@@ -30437,7 +30705,7 @@
       <c r="AT962" s="3"/>
       <c r="AU962" s="3"/>
     </row>
-    <row r="963" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
@@ -30464,7 +30732,7 @@
       <c r="AT963" s="3"/>
       <c r="AU963" s="3"/>
     </row>
-    <row r="964" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
@@ -30491,7 +30759,7 @@
       <c r="AT964" s="3"/>
       <c r="AU964" s="3"/>
     </row>
-    <row r="965" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
@@ -30518,7 +30786,7 @@
       <c r="AT965" s="3"/>
       <c r="AU965" s="3"/>
     </row>
-    <row r="966" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
@@ -30545,7 +30813,7 @@
       <c r="AT966" s="3"/>
       <c r="AU966" s="3"/>
     </row>
-    <row r="967" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
@@ -30572,7 +30840,7 @@
       <c r="AT967" s="3"/>
       <c r="AU967" s="3"/>
     </row>
-    <row r="968" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
@@ -30599,7 +30867,7 @@
       <c r="AT968" s="3"/>
       <c r="AU968" s="3"/>
     </row>
-    <row r="969" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
@@ -30626,7 +30894,7 @@
       <c r="AT969" s="3"/>
       <c r="AU969" s="3"/>
     </row>
-    <row r="970" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
@@ -30653,7 +30921,7 @@
       <c r="AT970" s="3"/>
       <c r="AU970" s="3"/>
     </row>
-    <row r="971" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
@@ -30680,7 +30948,7 @@
       <c r="AT971" s="3"/>
       <c r="AU971" s="3"/>
     </row>
-    <row r="972" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
@@ -30707,7 +30975,7 @@
       <c r="AT972" s="3"/>
       <c r="AU972" s="3"/>
     </row>
-    <row r="973" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
@@ -30734,7 +31002,7 @@
       <c r="AT973" s="3"/>
       <c r="AU973" s="3"/>
     </row>
-    <row r="974" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
@@ -30761,7 +31029,7 @@
       <c r="AT974" s="3"/>
       <c r="AU974" s="3"/>
     </row>
-    <row r="975" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
@@ -30788,7 +31056,7 @@
       <c r="AT975" s="3"/>
       <c r="AU975" s="3"/>
     </row>
-    <row r="976" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
@@ -30815,7 +31083,7 @@
       <c r="AT976" s="3"/>
       <c r="AU976" s="3"/>
     </row>
-    <row r="977" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
@@ -30842,7 +31110,7 @@
       <c r="AT977" s="3"/>
       <c r="AU977" s="3"/>
     </row>
-    <row r="978" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
@@ -30869,7 +31137,7 @@
       <c r="AT978" s="3"/>
       <c r="AU978" s="3"/>
     </row>
-    <row r="979" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
@@ -30896,7 +31164,7 @@
       <c r="AT979" s="3"/>
       <c r="AU979" s="3"/>
     </row>
-    <row r="980" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
@@ -30923,7 +31191,7 @@
       <c r="AT980" s="3"/>
       <c r="AU980" s="3"/>
     </row>
-    <row r="981" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
@@ -30950,7 +31218,7 @@
       <c r="AT981" s="3"/>
       <c r="AU981" s="3"/>
     </row>
-    <row r="982" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
@@ -30977,7 +31245,7 @@
       <c r="AT982" s="3"/>
       <c r="AU982" s="3"/>
     </row>
-    <row r="983" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
@@ -31004,7 +31272,7 @@
       <c r="AT983" s="3"/>
       <c r="AU983" s="3"/>
     </row>
-    <row r="984" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
@@ -31031,7 +31299,7 @@
       <c r="AT984" s="3"/>
       <c r="AU984" s="3"/>
     </row>
-    <row r="985" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
@@ -31058,7 +31326,7 @@
       <c r="AT985" s="3"/>
       <c r="AU985" s="3"/>
     </row>
-    <row r="986" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
@@ -31085,7 +31353,7 @@
       <c r="AT986" s="3"/>
       <c r="AU986" s="3"/>
     </row>
-    <row r="987" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
@@ -31112,7 +31380,7 @@
       <c r="AT987" s="3"/>
       <c r="AU987" s="3"/>
     </row>
-    <row r="988" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
@@ -31139,7 +31407,7 @@
       <c r="AT988" s="3"/>
       <c r="AU988" s="3"/>
     </row>
-    <row r="989" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
@@ -31166,7 +31434,7 @@
       <c r="AT989" s="3"/>
       <c r="AU989" s="3"/>
     </row>
-    <row r="990" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
@@ -31193,7 +31461,7 @@
       <c r="AT990" s="3"/>
       <c r="AU990" s="3"/>
     </row>
-    <row r="991" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
@@ -31220,7 +31488,7 @@
       <c r="AT991" s="3"/>
       <c r="AU991" s="3"/>
     </row>
-    <row r="992" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
@@ -31247,7 +31515,7 @@
       <c r="AT992" s="3"/>
       <c r="AU992" s="3"/>
     </row>
-    <row r="993" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
@@ -31274,7 +31542,7 @@
       <c r="AT993" s="3"/>
       <c r="AU993" s="3"/>
     </row>
-    <row r="994" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
@@ -31301,7 +31569,7 @@
       <c r="AT994" s="3"/>
       <c r="AU994" s="3"/>
     </row>
-    <row r="995" spans="1:47" ht="16" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:47" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
